--- a/src/attributions/attributions_saliency_traj_334.xlsx
+++ b/src/attributions/attributions_saliency_traj_334.xlsx
@@ -999,2847 +999,2847 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2.341810613870621e-05</v>
+        <v>0.03095665760338306</v>
       </c>
       <c r="B2" t="n">
-        <v>0.03499239310622215</v>
+        <v>0.1069695353507996</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00350286578759551</v>
+        <v>0.01236569881439209</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0230090506374836</v>
+        <v>0.1143952831625938</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008925957605242729</v>
+        <v>0.04940759018063545</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006012598983943462</v>
+        <v>0.04737821593880653</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001151922973804176</v>
+        <v>0.0221596360206604</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0003377640387043357</v>
+        <v>0.03652754426002502</v>
       </c>
       <c r="I2" t="n">
-        <v>3.456952981650829e-06</v>
+        <v>0.003002418670803308</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008665836649015546</v>
+        <v>0.06378220021724701</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02816659025847912</v>
+        <v>0.08008532226085663</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005777219776064157</v>
+        <v>0.03575633093714714</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01501764636486769</v>
+        <v>0.1680211424827576</v>
       </c>
       <c r="N2" t="n">
-        <v>0.007022694684565067</v>
+        <v>0.07504600286483765</v>
       </c>
       <c r="O2" t="n">
-        <v>0.006089435890316963</v>
+        <v>0.03586434200406075</v>
       </c>
       <c r="P2" t="n">
-        <v>0.002787757897749543</v>
+        <v>0.03321380168199539</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00556863471865654</v>
+        <v>0.009064006619155407</v>
       </c>
       <c r="R2" t="n">
-        <v>0.002981290454044938</v>
+        <v>0.0007598827360197902</v>
       </c>
       <c r="S2" t="n">
-        <v>5.725125083699822e-05</v>
+        <v>0.01739982701838017</v>
       </c>
       <c r="T2" t="n">
-        <v>0.005077056121081114</v>
+        <v>0.02104320377111435</v>
       </c>
       <c r="U2" t="n">
-        <v>0.001729178242385387</v>
+        <v>0.006930860690772533</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0008205408230423927</v>
+        <v>0.01371458917856216</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002578513463959098</v>
+        <v>0.0188435111194849</v>
       </c>
       <c r="X2" t="n">
-        <v>0.005666118115186691</v>
+        <v>0.006124740932136774</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.00582405086606741</v>
+        <v>0.008471239358186722</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001106647774577141</v>
+        <v>0.003936306107789278</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.001594908651895821</v>
+        <v>0.001794066862203181</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.005187574308365583</v>
+        <v>0.01755336485803127</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.004225984681397676</v>
+        <v>0.02766831591725349</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.0003158131148666143</v>
+        <v>0.008780280128121376</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.0009602362988516688</v>
+        <v>0.007261580787599087</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.003168180817738175</v>
+        <v>0.01752632856369019</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.002853598911315203</v>
+        <v>0.009649298153817654</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.094245377928019e-05</v>
+        <v>0.006566612515598536</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.001320023671723902</v>
+        <v>0.002765492536127567</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.001559932949021459</v>
+        <v>0.01050758082419634</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.001238548429682851</v>
+        <v>0.01766091585159302</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.004114249255508184</v>
+        <v>0.03673452883958817</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.0006626555696129799</v>
+        <v>0.01211793720722198</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.0009105299832299352</v>
+        <v>0.003518464043736458</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.0005178399151191115</v>
+        <v>0.001464969245716929</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.003472315846011043</v>
+        <v>0.0289660319685936</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.001055970555171371</v>
+        <v>0.01323296874761581</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.0009765505674295127</v>
+        <v>0.002610256429761648</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.002564979251474142</v>
+        <v>0.02402730286121368</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.003898925613611937</v>
+        <v>0.01967364735901356</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.02145947888493538</v>
+        <v>0.0757565051317215</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.227421833202243e-05</v>
+        <v>0.01661420427262783</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.01334068737924099</v>
+        <v>0.07250653952360153</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.003122083842754364</v>
+        <v>0.06016640737652779</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.0004555494524538517</v>
+        <v>0.01257280353456736</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.005840055644512177</v>
+        <v>0.004285752773284912</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.003757879137992859</v>
+        <v>0.005489327944815159</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.002079370664432645</v>
+        <v>0.03022224456071854</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.355721805244684e-05</v>
+        <v>0.008163748309016228</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.007216079626232386</v>
+        <v>0.004635831341147423</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.004260080866515636</v>
+        <v>0.02284270897507668</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0002628124784678221</v>
+        <v>0.01773917488753796</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.00783015601336956</v>
+        <v>0.01306712627410889</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0007518798811361194</v>
+        <v>0.02100722678005695</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.003702030749991536</v>
+        <v>0.001341110095381737</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.00334909139201045</v>
+        <v>0.01974861323833466</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.002539355074986815</v>
+        <v>0.02521383762359619</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.00507673341780901</v>
+        <v>0.005210948642343283</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0005645662313327193</v>
+        <v>0.008753051981329918</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.001138536375947297</v>
+        <v>0.02829502150416374</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0004899894120171666</v>
+        <v>0.00851934403181076</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.00264056259766221</v>
+        <v>0.02699804306030273</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.002570886397734284</v>
+        <v>0.0003634770982898772</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.00187645317055285</v>
+        <v>0.01106949895620346</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.001281268894672394</v>
+        <v>0.009482781402766705</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.001063962001353502</v>
+        <v>0.004982973914593458</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.002906845416873693</v>
+        <v>0.01548940408974886</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.01189185492694378</v>
+        <v>0.06476706266403198</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.002237197477370501</v>
+        <v>0.006319760344922543</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.00455652829259634</v>
+        <v>0.04872430488467216</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0007818071753717959</v>
+        <v>0.02719159796833992</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.002764341654255986</v>
+        <v>0.01606318913400173</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.049264730885625e-05</v>
+        <v>0.01449553389102221</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.002942812396213412</v>
+        <v>0.002044067485257983</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.001799306366592646</v>
+        <v>0.003864043159410357</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.001057995716109872</v>
+        <v>0.0040098512545228</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.004801428876817226</v>
+        <v>0.02923921309411526</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.0007826173678040504</v>
+        <v>0.003634605556726456</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.003236125921830535</v>
+        <v>0.03506952524185181</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.001449619303457439</v>
+        <v>0.004706812556833029</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.001218828023411334</v>
+        <v>0.0006951816030777991</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.001437288825400174</v>
+        <v>0.003120495937764645</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.000266631948761642</v>
+        <v>0.01089795213192701</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.0005148930358700454</v>
+        <v>0.004271768964827061</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.004769615828990936</v>
+        <v>0.005540226586163044</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.0009755566716194153</v>
+        <v>0.0459737703204155</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0005404531839303672</v>
+        <v>0.005268418230116367</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.003957973793148994</v>
+        <v>0.0344279482960701</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.005745569709688425</v>
+        <v>0.007905619218945503</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.004070258233696222</v>
+        <v>0.01772807165980339</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.0028067696839571</v>
+        <v>0.001153560820966959</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.009378658607602119</v>
+        <v>0.0141615578904748</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.002210773061960936</v>
+        <v>0.002793235471472144</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0005640294984914362</v>
+        <v>0.006238453090190887</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.005032023880630732</v>
+        <v>0.03020010516047478</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.00128482049331069</v>
+        <v>0.007317365612834692</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.004466217011213303</v>
+        <v>0.03802118822932243</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.001198186306282878</v>
+        <v>0.006322424858808517</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.002779456786811352</v>
+        <v>0.002202594885602593</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.0009271397138945758</v>
+        <v>0.003114697523415089</v>
       </c>
       <c r="DC2" t="n">
-        <v>8.30658245831728e-06</v>
+        <v>0.01016165968030691</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.0001771207898855209</v>
+        <v>0.004917027428746223</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.001364619005471468</v>
+        <v>0.03291688859462738</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.009023024700582027</v>
+        <v>0.0480099618434906</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.0002830817538779229</v>
+        <v>0.0579197108745575</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01420744322240353</v>
+        <v>0.0366092249751091</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.004222793038934469</v>
+        <v>0.01266494952142239</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.0003910726809408516</v>
+        <v>0.03051369450986385</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.002357754157856107</v>
+        <v>0.009511825628578663</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.00413748063147068</v>
+        <v>0.04660253599286079</v>
       </c>
       <c r="DM2" t="n">
-        <v>0.001955676358193159</v>
+        <v>0.009467964991927147</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.003067679237574339</v>
+        <v>0.02779150381684303</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.003369262907654047</v>
+        <v>0.01896445825695992</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.004490737337619066</v>
+        <v>0.01296535693109035</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.00213446537964046</v>
+        <v>0.02806011214852333</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.002394437789916992</v>
+        <v>0.01942564733326435</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.001337074907496572</v>
+        <v>0.0247006993740797</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.0003936943248845637</v>
+        <v>0.01465025823563337</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.0001723594614304602</v>
+        <v>0.003955626860260963</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.0007736487314105034</v>
+        <v>0.03071087040007114</v>
       </c>
       <c r="DW2" t="n">
-        <v>9.497429709881544e-05</v>
+        <v>0.01651938445866108</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.0007630360778421164</v>
+        <v>0.01136381458491087</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.003249796340242028</v>
+        <v>0.00576300360262394</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.001516721677035093</v>
+        <v>0.02328654006123543</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.002911905758082867</v>
+        <v>0.01899951882660389</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.002530169207602739</v>
+        <v>0.001382860820740461</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.001954095205292106</v>
+        <v>0.01104284357279539</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.0004084235697519034</v>
+        <v>0.05912698432803154</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.0004603852285072207</v>
+        <v>0.03719391673803329</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.001116588478907943</v>
+        <v>0.02760522067546844</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.004478190094232559</v>
+        <v>0.0220381747931242</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.001130701624788344</v>
+        <v>0.001196736469864845</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.007152456790208817</v>
+        <v>0.04264499992132187</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.003801153972744942</v>
+        <v>0.004113968927413225</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.002973789349198341</v>
+        <v>0.003028686856850982</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.001584701472893357</v>
+        <v>0.00598874781280756</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.001569560030475259</v>
+        <v>0.005731923040002584</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.000607463822234422</v>
+        <v>0.003739082720130682</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.001390978344716132</v>
+        <v>0.002808356191962957</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.003945158794522285</v>
+        <v>0.03535623103380203</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.002904789056628942</v>
+        <v>0.009137476794421673</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.001702213776297867</v>
+        <v>0.007573356386274099</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.001937142806127667</v>
+        <v>0.004188157618045807</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.005966497119516134</v>
+        <v>0.02605423144996166</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.0007344472105614841</v>
+        <v>0.01396914012730122</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.002656307071447372</v>
+        <v>0.01110063120722771</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.001526055275462568</v>
+        <v>0.02150985971093178</v>
       </c>
       <c r="EX2" t="n">
-        <v>4.378202720545232e-05</v>
+        <v>0.001323615666478872</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.005214080680161715</v>
+        <v>0.03289132937788963</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.0002012468612520024</v>
+        <v>0.002370674163103104</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.003893827321007848</v>
+        <v>0.03939235955476761</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.001216028584167361</v>
+        <v>0.005778464488685131</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.00272205239161849</v>
+        <v>0.003082255367189646</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.001172640710137784</v>
+        <v>7.726135663688183e-05</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.0001107965363189578</v>
+        <v>0.01350283063948154</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.0004105645348317921</v>
+        <v>0.006655252538621426</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.0005334732122719288</v>
+        <v>0.001809419132769108</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.001754774712026119</v>
+        <v>0.004020320251584053</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.0005976048996672034</v>
+        <v>0.01326865330338478</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.003942473791539669</v>
+        <v>0.00228684488683939</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.0009737382060848176</v>
+        <v>0.01956245675683022</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.001756684156134725</v>
+        <v>0.0009541953913867474</v>
       </c>
       <c r="FM2" t="n">
-        <v>0.003237124532461166</v>
+        <v>0.01540161855518818</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.002478699898347259</v>
+        <v>0.02854540944099426</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.003418728243559599</v>
+        <v>0.003453564131632447</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.0002987718908116221</v>
+        <v>0.01359892077744007</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.001667162403464317</v>
+        <v>0.05465978756546974</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.002157350070774555</v>
+        <v>0.01207839418202639</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.0002285319205839187</v>
+        <v>0.05405322462320328</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.002674331655725837</v>
+        <v>0.05448340624570847</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.0009200565982609987</v>
+        <v>0.02051321044564247</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.002775721717625856</v>
+        <v>0.00904382299631834</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.003216627286747098</v>
+        <v>0.01144797913730145</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.002533925930038095</v>
+        <v>0.04365319386124611</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.002157902577891946</v>
+        <v>0.01018426194787025</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.002245191484689713</v>
+        <v>0.0248011089861393</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.0007457621395587921</v>
+        <v>0.01943765580654144</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.0005887830047868192</v>
+        <v>0.01835893839597702</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.005728909745812416</v>
+        <v>0.04950303211808205</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.00280745979398489</v>
+        <v>0.000244067283347249</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.005830236244946718</v>
+        <v>0.03007752075791359</v>
       </c>
       <c r="GF2" t="n">
-        <v>7.549941074103117e-05</v>
+        <v>7.581873796880245e-05</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.0009075701818801463</v>
+        <v>0.003419219749048352</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.3762063384056091</v>
+        <v>0.0390223003923893</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1523477584123611</v>
+        <v>0.006814016494899988</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4456992149353027</v>
+        <v>0.01604421436786652</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05339531600475311</v>
+        <v>0.01229028310626745</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1161372736096382</v>
+        <v>0.01529540866613388</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09392644464969635</v>
+        <v>0.01202508248388767</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2671577334403992</v>
+        <v>0.005280266050249338</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01708373986184597</v>
+        <v>0.02217289805412292</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1039918214082718</v>
+        <v>0.006904059089720249</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1025238111615181</v>
+        <v>0.04861533269286156</v>
       </c>
       <c r="K3" t="n">
-        <v>0.06450726836919785</v>
+        <v>0.007748065982013941</v>
       </c>
       <c r="L3" t="n">
-        <v>0.372563898563385</v>
+        <v>0.008537102490663528</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1360463947057724</v>
+        <v>0.007724818773567677</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05035097151994705</v>
+        <v>0.03675619140267372</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06676137447357178</v>
+        <v>0.008853701874613762</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2082677483558655</v>
+        <v>0.007341598160564899</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03398185968399048</v>
+        <v>0.02247290313243866</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1294408291578293</v>
+        <v>0.001587039791047573</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1129321753978729</v>
+        <v>0.0001472667790949345</v>
       </c>
       <c r="T3" t="n">
-        <v>0.03351964801549911</v>
+        <v>0.01837535388767719</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01301057823002338</v>
+        <v>0.002362983766943216</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09435350447893143</v>
+        <v>0.006876321043819189</v>
       </c>
       <c r="W3" t="n">
-        <v>0.09638654440641403</v>
+        <v>0.003316960763186216</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0456879623234272</v>
+        <v>0.003874811809509993</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0007467214018106461</v>
+        <v>0.0002363577368669212</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1046696528792381</v>
+        <v>0.002612825715914369</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.06290864199399948</v>
+        <v>0.0008395384647883475</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.06295470148324966</v>
+        <v>0.01870473474264145</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.08177100121974945</v>
+        <v>0.0004891632706858218</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.02268220484256744</v>
+        <v>0.003728536423295736</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.0007211565971374512</v>
+        <v>0.00911508034914732</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1211233586072922</v>
+        <v>0.009490423835813999</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.006333883851766586</v>
+        <v>0.01034308224916458</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.03897169977426529</v>
+        <v>0.0006156992167234421</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.02914624661207199</v>
+        <v>0.008238382637500763</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.03775694593787193</v>
+        <v>0.002786273136734962</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02768127992749214</v>
+        <v>0.006544871255755424</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.005091607570648193</v>
+        <v>0.01913099735975266</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.01266189571470022</v>
+        <v>0.001599546754732728</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.07477647811174393</v>
+        <v>0.001524194842204452</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.06888219714164734</v>
+        <v>0.004417483694851398</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.01622950285673141</v>
+        <v>0.0003712640609592199</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.06782852113246918</v>
+        <v>3.329067840240896e-05</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.09181337058544159</v>
+        <v>0.01026787515729666</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.03419870510697365</v>
+        <v>0.002225126372650266</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.2379221171140671</v>
+        <v>0.03050395846366882</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.1676720976829529</v>
+        <v>0.01420133654028177</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3807923793792725</v>
+        <v>0.007707252167165279</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.01845467090606689</v>
+        <v>0.009005606174468994</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.5131241083145142</v>
+        <v>0.01381499320268631</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.1099772900342941</v>
+        <v>0.01049680914729834</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.253631979227066</v>
+        <v>1.853215508162975e-05</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.2319992929697037</v>
+        <v>0.01256859302520752</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.1497056931257248</v>
+        <v>0.002748337807133794</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.2219114452600479</v>
+        <v>0.008048791438341141</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.00611460953950882</v>
+        <v>0.007948278449475765</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0007892847061157227</v>
+        <v>0.000994883244857192</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.2090841978788376</v>
+        <v>0.005359681323170662</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.09875372052192688</v>
+        <v>0.0215805359184742</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.1864782869815826</v>
+        <v>0.007566919550299644</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.05669611692428589</v>
+        <v>0.008721813559532166</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.01143088936805725</v>
+        <v>0.01555492449551821</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.01365166343748569</v>
+        <v>0.0009231055155396461</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.1080433800816536</v>
+        <v>0.007255847565829754</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1456301063299179</v>
+        <v>0.0005429222946986556</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.04501613229513168</v>
+        <v>0.0008134074159897864</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.07911130040884018</v>
+        <v>0.008598269894719124</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0539766363799572</v>
+        <v>2.944236621260643e-05</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.08952038735151291</v>
+        <v>0.001251192064955831</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.2116063386201859</v>
+        <v>0.003186459885910153</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1277921795845032</v>
+        <v>0.0004084890242666006</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1904345452785492</v>
+        <v>0.003209367860108614</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1256178319454193</v>
+        <v>0.01646676100790501</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.1482463777065277</v>
+        <v>0.00918186828494072</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.2068023979663849</v>
+        <v>0.006528906524181366</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.0378769114613533</v>
+        <v>0.004032524302601814</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.2635260224342346</v>
+        <v>0.01835183426737785</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.2145286649465561</v>
+        <v>0.0001235586823895574</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.05954504013061523</v>
+        <v>0.0004094568430446088</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.01191509887576103</v>
+        <v>0.00158809230197221</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.02441299706697464</v>
+        <v>0.003986354451626539</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.06956469267606735</v>
+        <v>0.009761220775544643</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.08672112226486206</v>
+        <v>0.002426477149128914</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.03696941584348679</v>
+        <v>0.002043729647994041</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.06298027187585831</v>
+        <v>0.004553153645247221</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0240973737090826</v>
+        <v>0.01161373592913151</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.02611097134649754</v>
+        <v>0.003779391059651971</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.05477939546108246</v>
+        <v>0.00211626198142767</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.03001148626208305</v>
+        <v>0.0009528734954074025</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.04014743492007256</v>
+        <v>0.002525145187973976</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.1283020824193954</v>
+        <v>0.001059580594301224</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.02814726531505585</v>
+        <v>0.0107797896489501</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.04987601190805435</v>
+        <v>0.002951713046059012</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.2064740806818008</v>
+        <v>0.01721277460455894</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.4227727651596069</v>
+        <v>0.002500473521649837</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.01385780796408653</v>
+        <v>0.002566575072705746</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.05645442754030228</v>
+        <v>0.01111963670700788</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.00502402801066637</v>
+        <v>0.005302316509187222</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.06319369375705719</v>
+        <v>0.005201066844165325</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.02722303196787834</v>
+        <v>0.01081353519111872</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.1157102361321449</v>
+        <v>0.004690810572355986</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0374845564365387</v>
+        <v>0.003712444566190243</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.05224917083978653</v>
+        <v>0.0030233149882406</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.02466215007007122</v>
+        <v>0.009369947016239166</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.02827360667288303</v>
+        <v>0.004399956203997135</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.05228615552186966</v>
+        <v>0.001602033386006951</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.0503368191421032</v>
+        <v>0.001708800322376192</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.01309169270098209</v>
+        <v>0.002756660338491201</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0471593514084816</v>
+        <v>0.0007399162277579308</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.08499395847320557</v>
+        <v>0.01082869432866573</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.1512821614742279</v>
+        <v>0.005042447242885828</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.3929121494293213</v>
+        <v>0.002852542093023658</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.3250589668750763</v>
+        <v>0.008194070309400558</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.03738652169704437</v>
+        <v>0.008688973262906075</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.05779564380645752</v>
+        <v>0.001264318590983748</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.186270073056221</v>
+        <v>0.004274987615644932</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.09824785590171814</v>
+        <v>0.01064420863986015</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.1339868605136871</v>
+        <v>0.00443585216999054</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.2193532288074493</v>
+        <v>0.0007284901803359389</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.01904547773301601</v>
+        <v>0.001371498103253543</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.03491316735744476</v>
+        <v>0.0009013322414830327</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1305396109819412</v>
+        <v>0.005404438823461533</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.105879932641983</v>
+        <v>0.003970728255808353</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.01462265662848949</v>
+        <v>0.001296507893130183</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.008199125528335571</v>
+        <v>0.001181151252239943</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.09718373417854309</v>
+        <v>0.0002121783327311277</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0120015749707818</v>
+        <v>0.00580362044274807</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.137972354888916</v>
+        <v>0.008182673715054989</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.0456664077937603</v>
+        <v>0.003529968671500683</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.06366577744483948</v>
+        <v>0.00367680424824357</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.2151485979557037</v>
+        <v>0.01042130030691624</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.137861430644989</v>
+        <v>0.005430122837424278</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.05025263875722885</v>
+        <v>0.007932531647384167</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.006090858019888401</v>
+        <v>0.0004588421434164047</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.001708036055788398</v>
+        <v>0.008273158222436905</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.03637662902474403</v>
+        <v>0.00752998236566782</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.07197762280702591</v>
+        <v>0.006817089859396219</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.1067768484354019</v>
+        <v>0.004022375680506229</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.129320353269577</v>
+        <v>0.001685635885223746</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.00149375875480473</v>
+        <v>0.01289011724293232</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.09605944901704788</v>
+        <v>0.002221530769020319</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.09370016306638718</v>
+        <v>0.003522394690662622</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.01609477959573269</v>
+        <v>0.001759356120601296</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.02908897958695889</v>
+        <v>0.001002831035293639</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.1323047429323196</v>
+        <v>0.001368906581774354</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.04523291438817978</v>
+        <v>0.004011991899460554</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.000765814445912838</v>
+        <v>0.006383522879332304</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.07531066238880157</v>
+        <v>0.006667324341833591</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.1844715625047684</v>
+        <v>0.004212537780404091</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.02406045794487</v>
+        <v>0.004822593182325363</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.1757588684558868</v>
+        <v>0.003211141098290682</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.05575130507349968</v>
+        <v>0.001116924453526735</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.2280275076627731</v>
+        <v>0.003052267478778958</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.02409801259636879</v>
+        <v>0.0108002033084631</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.07757309824228287</v>
+        <v>0.004010948818176985</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.03994359821081161</v>
+        <v>0.005664502736181021</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.03947469219565392</v>
+        <v>0.002599098486825824</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.04715057462453842</v>
+        <v>0.01170857716351748</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.0007227312889881432</v>
+        <v>0.004194325767457485</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.08318901062011719</v>
+        <v>0.001850975793786347</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.07904089987277985</v>
+        <v>0.002143512014299631</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.00698442105203867</v>
+        <v>0.004652822390198708</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.05723696202039719</v>
+        <v>0.0217418298125267</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.1012265756726265</v>
+        <v>0.006337530910968781</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.09193895012140274</v>
+        <v>0.005093731917440891</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.02630619332194328</v>
+        <v>0.01052429806441069</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.07931829988956451</v>
+        <v>0.01260932348668575</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.1305259615182877</v>
+        <v>0.00859073456376791</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.1817006170749664</v>
+        <v>0.004685061518102884</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.08997432142496109</v>
+        <v>8.74687684699893e-05</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.03273211419582367</v>
+        <v>0.0001494027674198151</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.2242487370967865</v>
+        <v>0.02063389681279659</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.1406024098396301</v>
+        <v>0.03137516975402832</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.0195268914103508</v>
+        <v>0.02240598015487194</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.09356886893510818</v>
+        <v>0.004149159882217646</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.1392427682876587</v>
+        <v>0.00722791999578476</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.1529621183872223</v>
+        <v>0.01382634043693542</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.1540876924991608</v>
+        <v>0.002945293672382832</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.02631546929478645</v>
+        <v>0.005865106359124184</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.04371625557541847</v>
+        <v>0.001391045516356826</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.02504165656864643</v>
+        <v>0.01179786771535873</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.0432421937584877</v>
+        <v>0.01387287117540836</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1033270880579948</v>
+        <v>0.006123327650129795</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.03839093819260597</v>
+        <v>0.0004044316592626274</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.1054514050483704</v>
+        <v>0.004052887205034494</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.1931304186582565</v>
+        <v>0.01849791035056114</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.1690956652164459</v>
+        <v>0.007157487794756889</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.1338286399841309</v>
+        <v>0.001205344218760729</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.01772056706249714</v>
+        <v>0.001264886581338942</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0006621781503781676</v>
+        <v>0.0677679255604744</v>
       </c>
       <c r="B4" t="n">
-        <v>0.00873840507119894</v>
+        <v>0.4077847301959991</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0005369972786866128</v>
+        <v>0.03058139979839325</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00111381255555898</v>
+        <v>0.01525337249040604</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008095615776255727</v>
+        <v>0.03360817581415176</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005385197233408689</v>
+        <v>0.6424682140350342</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006923343171365559</v>
+        <v>0.08475635200738907</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001653087558224797</v>
+        <v>0.1732536554336548</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006630038842558861</v>
+        <v>0.0120187783613801</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001272766850888729</v>
+        <v>0.03581754118204117</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007207863498479128</v>
+        <v>0.4611871838569641</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002034454373642802</v>
+        <v>0.0219300240278244</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002314340323209763</v>
+        <v>0.01063396222889423</v>
       </c>
       <c r="N4" t="n">
-        <v>0.001307128579355776</v>
+        <v>0.1734901666641235</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005124906077980995</v>
+        <v>0.5453312397003174</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0008499558316543698</v>
+        <v>0.005833468399941921</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001811825204640627</v>
+        <v>0.1185795292258263</v>
       </c>
       <c r="R4" t="n">
-        <v>6.843771552667022e-05</v>
+        <v>0.01635528542101383</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0003859850985463709</v>
+        <v>0.08984252065420151</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00138924119528383</v>
+        <v>0.08115701377391815</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0007400350295938551</v>
+        <v>0.17497518658638</v>
       </c>
       <c r="V4" t="n">
-        <v>3.807734901783988e-05</v>
+        <v>0.008510089479386806</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0004687987093348056</v>
+        <v>0.07337988913059235</v>
       </c>
       <c r="X4" t="n">
-        <v>0.001426119008101523</v>
+        <v>0.1436633914709091</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0003874748945236206</v>
+        <v>0.1355743408203125</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0004910670686513186</v>
+        <v>0.07596370577812195</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0004541141097433865</v>
+        <v>0.0002149140927940607</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0003845816536340863</v>
+        <v>0.1069425344467163</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.001310267485678196</v>
+        <v>0.1616110503673553</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0004841748450417072</v>
+        <v>0.05718890577554703</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.672369009815156e-05</v>
+        <v>0.1961153447628021</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0001916394103318453</v>
+        <v>0.01350927911698818</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0005896557122468948</v>
+        <v>0.1372587084770203</v>
       </c>
       <c r="AH4" t="n">
-        <v>8.468941086903214e-05</v>
+        <v>0.05635632202029228</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.0007886429666541517</v>
+        <v>0.2163160741329193</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.0002688462845981121</v>
+        <v>0.1189279034733772</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0002849096490535885</v>
+        <v>0.0239194892346859</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001240374287590384</v>
+        <v>0.09013623744249344</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.0004100380465388298</v>
+        <v>0.02013041824102402</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.000722855213098228</v>
+        <v>0.03762058541178703</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.0003259155200794339</v>
+        <v>0.03261731564998627</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001052239560522139</v>
+        <v>0.1141698807477951</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.000205246004043147</v>
+        <v>0.1228242293000221</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0003939752350561321</v>
+        <v>0.09492465853691101</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0007312289671972394</v>
+        <v>0.0798582062125206</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.0008711567497812212</v>
+        <v>0.06088962405920029</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.006507457699626684</v>
+        <v>0.392474502325058</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.0003283557016402483</v>
+        <v>0.09872837364673615</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.001053066924214363</v>
+        <v>0.03419668972492218</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001306201564148068</v>
+        <v>0.2315237820148468</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002380199730396271</v>
+        <v>0.2975260615348816</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0001480882783653215</v>
+        <v>0.1072845607995987</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.0009027812629938126</v>
+        <v>0.02071964740753174</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0005727718234993517</v>
+        <v>0.02441999129951</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.426824696362019e-05</v>
+        <v>0.05821051076054573</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001502520986832678</v>
+        <v>0.06005164608359337</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001604411518201232</v>
+        <v>0.1054353713989258</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0001637066598050296</v>
+        <v>0.1518095284700394</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.003157970029860735</v>
+        <v>0.06893613934516907</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.002920438535511494</v>
+        <v>0.1545416414737701</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0006029997603036463</v>
+        <v>0.09212875366210938</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0004915316239930689</v>
+        <v>0.1206068620085716</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0002365717082284391</v>
+        <v>0.1070647463202477</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0001434518198948354</v>
+        <v>0.058334119617939</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0001266169274458662</v>
+        <v>0.0599101148545742</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0005545559688471258</v>
+        <v>0.02097370661795139</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0005429370212368667</v>
+        <v>0.07022762298583984</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0002465476864017546</v>
+        <v>0.03893964365124702</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0006914802361279726</v>
+        <v>0.1147893443703651</v>
       </c>
       <c r="BR4" t="n">
-        <v>3.0570721719414e-05</v>
+        <v>0.1458708941936493</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.00141199491918087</v>
+        <v>0.00344589538872242</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001239792443811893</v>
+        <v>0.06662990897893906</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0007862197235226631</v>
+        <v>0.05511400103569031</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.003268353175371885</v>
+        <v>0.1240466833114624</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001977775245904922</v>
+        <v>0.141156941652298</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0009771543554961681</v>
+        <v>0.03276088833808899</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.0003525506472215056</v>
+        <v>0.139448806643486</v>
       </c>
       <c r="BZ4" t="n">
-        <v>7.937924237921834e-05</v>
+        <v>0.3009636700153351</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.000461770046968013</v>
+        <v>0.2056635767221451</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.0005608433857560158</v>
+        <v>0.032671969383955</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.0004450948326848447</v>
+        <v>0.05382319539785385</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.0002842271060217172</v>
+        <v>0.01792654953896999</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.001539596007205546</v>
+        <v>0.1462382078170776</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.0004838787717744708</v>
+        <v>0.01571291498839855</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.0007756754057481885</v>
+        <v>0.002573350444436073</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.0005954245571047068</v>
+        <v>0.03785427659749985</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.0008200209122151136</v>
+        <v>0.1432717889547348</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0006072131218388677</v>
+        <v>0.03805844858288765</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0001472513395128772</v>
+        <v>0.05844492465257645</v>
       </c>
       <c r="CL4" t="n">
-        <v>7.030086999293417e-05</v>
+        <v>0.005435305647552013</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001377980457618833</v>
+        <v>0.0786435529589653</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001172001124359667</v>
+        <v>0.23638516664505</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.0001768142537912354</v>
+        <v>0.2247596979141235</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.001351780956611037</v>
+        <v>0.2059137672185898</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.0002918700920417905</v>
+        <v>0.100725919008255</v>
       </c>
       <c r="CR4" t="n">
-        <v>2.791247243294492e-05</v>
+        <v>0.1238219887018204</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.001695432234555483</v>
+        <v>0.0180461797863245</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.001252070185728371</v>
+        <v>0.1101380363106728</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0007807539077475667</v>
+        <v>0.09004341065883636</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0001656851673033088</v>
+        <v>0.001971928402781487</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.00130846188403666</v>
+        <v>0.1337890923023224</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.0004827685770578682</v>
+        <v>0.01437291596084833</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.0009498863364569843</v>
+        <v>0.008097895421087742</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.000366239168215543</v>
+        <v>0.01522369496524334</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.001062720897607505</v>
+        <v>0.1379798650741577</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.000485170166939497</v>
+        <v>0.04347696527838707</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.0001258980191778392</v>
+        <v>0.02444909326732159</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.361725925467908e-05</v>
+        <v>0.01921163499355316</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.0001786018838174641</v>
+        <v>0.1691019833087921</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.0005489815375767648</v>
+        <v>0.06987977772951126</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0004586738941725343</v>
+        <v>0.1196916699409485</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0007368019432760775</v>
+        <v>0.07210607826709747</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0007341409218497574</v>
+        <v>0.0379798486828804</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0006855138926766813</v>
+        <v>0.2178322076797485</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0005452664918266237</v>
+        <v>0.07113829255104065</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0002987068728543818</v>
+        <v>0.135142982006073</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0007975600892677903</v>
+        <v>0.1669150590896606</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.0002331131690880284</v>
+        <v>0.02037755586206913</v>
       </c>
       <c r="DO4" t="n">
-        <v>8.54529207572341e-05</v>
+        <v>0.04448959976434708</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.0005150918732397258</v>
+        <v>0.02566604688763618</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0009216296020895243</v>
+        <v>0.07572686672210693</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.001074760453775525</v>
+        <v>0.0380408987402916</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.000465671910205856</v>
+        <v>0.04590199515223503</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.0007313422975130379</v>
+        <v>0.03006009757518768</v>
       </c>
       <c r="DU4" t="n">
-        <v>2.017572478507645e-05</v>
+        <v>0.02537485584616661</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0007028246182017028</v>
+        <v>0.003574460046365857</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0004784027114510536</v>
+        <v>0.05531810969114304</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0002552295045461506</v>
+        <v>0.09263024479150772</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.0006752873305231333</v>
+        <v>0.01282018795609474</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0006217357004061341</v>
+        <v>0.005859368480741978</v>
       </c>
       <c r="EA4" t="n">
-        <v>8.676864672452211e-05</v>
+        <v>0.01127583812922239</v>
       </c>
       <c r="EB4" t="n">
-        <v>7.3398114182055e-06</v>
+        <v>0.08921928703784943</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.000260782428085804</v>
+        <v>0.03061849065124989</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0008715060539543629</v>
+        <v>0.08201230317354202</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0003474094846751541</v>
+        <v>0.1606187671422958</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0002784648968372494</v>
+        <v>0.0480411984026432</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.000940428813919425</v>
+        <v>0.05720508843660355</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0002050449838861823</v>
+        <v>0.07408037781715393</v>
       </c>
       <c r="EI4" t="n">
-        <v>8.502510900143534e-05</v>
+        <v>0.01849299296736717</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.000669622968416661</v>
+        <v>0.03025060519576073</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.000873526674695313</v>
+        <v>0.1582803875207901</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0002930082264356315</v>
+        <v>0.01627053134143353</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0009696490596979856</v>
+        <v>0.009422712959349155</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0003061917959712446</v>
+        <v>0.008714414201676846</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.0001309018989559263</v>
+        <v>0.02241305261850357</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.001448447699658573</v>
+        <v>0.09736213088035583</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.0002475112851243466</v>
+        <v>0.105802059173584</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0005624102195724845</v>
+        <v>0.04657019674777985</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0003141261695418507</v>
+        <v>0.08289608359336853</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.001849790452979505</v>
+        <v>0.1261389702558517</v>
       </c>
       <c r="EU4" t="n">
-        <v>4.589405580190942e-05</v>
+        <v>0.00711653009057045</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0005058193346485496</v>
+        <v>0.01670380868017673</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001000330434180796</v>
+        <v>0.02059150859713554</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0001852440764196217</v>
+        <v>0.008859783411026001</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001325823133811355</v>
+        <v>0.139899343252182</v>
       </c>
       <c r="EZ4" t="n">
-        <v>9.246174886357039e-05</v>
+        <v>0.01282745972275734</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.0005784054519608617</v>
+        <v>0.01062438078224659</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.000264122529188171</v>
+        <v>0.05657076835632324</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.0008515044464729726</v>
+        <v>0.1405653804540634</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.000552603043615818</v>
+        <v>0.03609020262956619</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.0003434364916756749</v>
+        <v>0.0541776530444622</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.0001133881305577233</v>
+        <v>0.01577856950461864</v>
       </c>
       <c r="FG4" t="n">
-        <v>3.437813211348839e-05</v>
+        <v>0.07563142478466034</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.0006471381639130414</v>
+        <v>0.07251153886318207</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.0004644295549951494</v>
+        <v>0.05433838069438934</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.001627906109206378</v>
+        <v>0.01512081921100616</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.0006490794476121664</v>
+        <v>0.003752054646611214</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0002447169972583652</v>
+        <v>0.1846928894519806</v>
       </c>
       <c r="FM4" t="n">
-        <v>4.390611866256222e-05</v>
+        <v>0.08384628593921661</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.0007652799831703305</v>
+        <v>0.1094762608408928</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.0007131105521693826</v>
+        <v>0.1473521739244461</v>
       </c>
       <c r="FP4" t="n">
-        <v>4.657133104046807e-05</v>
+        <v>0.1682556718587875</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.00436528492718935</v>
+        <v>0.03239348903298378</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.0001695988612482324</v>
+        <v>0.01631627976894379</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.001277079922147095</v>
+        <v>0.1306681036949158</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.001109183998778462</v>
+        <v>0.09779611229896545</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.002668431727215648</v>
+        <v>0.1838360726833344</v>
       </c>
       <c r="FV4" t="n">
-        <v>6.989811663515866e-05</v>
+        <v>0.002420881763100624</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.0012696732301265</v>
+        <v>0.1549822688102722</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.0005333074368536472</v>
+        <v>0.04205698147416115</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.001081845257431269</v>
+        <v>0.1294274479150772</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.000615880184341222</v>
+        <v>0.03098952770233154</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.0001641765120439231</v>
+        <v>0.04523357748985291</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0001252676884178072</v>
+        <v>0.008456772193312645</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.002650352194905281</v>
+        <v>0.2385877221822739</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.00152233149856329</v>
+        <v>0.1626006364822388</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.001692059333436191</v>
+        <v>0.01283530704677105</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.0002672079717740417</v>
+        <v>0.01701200380921364</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.0005643540062010288</v>
+        <v>0.1657173931598663</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.01464190147817135</v>
+        <v>0.0006817099638283253</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7260693907737732</v>
+        <v>0.04573746025562286</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04604244604706764</v>
+        <v>0.01539946906268597</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3855218887329102</v>
+        <v>0.02772311493754387</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1430390775203705</v>
+        <v>0.002533243270590901</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02036083862185478</v>
+        <v>0.02942689135670662</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05851642414927483</v>
+        <v>0.01385991740971804</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006655104458332062</v>
+        <v>0.01592070609331131</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01446201093494892</v>
+        <v>0.001082391943782568</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06650861352682114</v>
+        <v>0.004051489289849997</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5850806832313538</v>
+        <v>0.04122859612107277</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0342872142791748</v>
+        <v>0.02124065905809402</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3815774917602539</v>
+        <v>0.04361853003501892</v>
       </c>
       <c r="N5" t="n">
-        <v>0.212374672293663</v>
+        <v>0.02142238803207874</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01139443926513195</v>
+        <v>0.03035284765064716</v>
       </c>
       <c r="P5" t="n">
-        <v>0.05707762762904167</v>
+        <v>0.01402170583605766</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1128460690379143</v>
+        <v>0.009850647300481796</v>
       </c>
       <c r="R5" t="n">
-        <v>0.05125806108117104</v>
+        <v>0.005216129124164581</v>
       </c>
       <c r="S5" t="n">
-        <v>0.07393677532672882</v>
+        <v>0.002759834285825491</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09533817321062088</v>
+        <v>0.0009322174591943622</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02957423217594624</v>
+        <v>0.004103398881852627</v>
       </c>
       <c r="V5" t="n">
-        <v>0.01900184154510498</v>
+        <v>0.003123296657577157</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01404176279902458</v>
+        <v>0.002098880242556334</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09077108651399612</v>
+        <v>0.01070814672857523</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09868042916059494</v>
+        <v>0.004115371964871883</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02856495045125484</v>
+        <v>0.001882002921774983</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03509474918246269</v>
+        <v>0.0045680096372962</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.03867786750197411</v>
+        <v>0.001083246665075421</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1468407958745956</v>
+        <v>0.008329516276717186</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.03893285989761353</v>
+        <v>0.008711800910532475</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.009342893958091736</v>
+        <v>0.003211432602256536</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.07385119050741196</v>
+        <v>0.0004847664386034012</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0301947183907032</v>
+        <v>0.02312243729829788</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.02549395151436329</v>
+        <v>0.005676340311765671</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0009674374014139175</v>
+        <v>0.01244252640753984</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.03291087597608566</v>
+        <v>0.005386629141867161</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.02812998741865158</v>
+        <v>0.001275852788239717</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.06717842072248459</v>
+        <v>0.01698709651827812</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0002267612144351006</v>
+        <v>0.009974559769034386</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.03022002428770065</v>
+        <v>0.003795781638473272</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.03078635036945343</v>
+        <v>0.006587551906704903</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.05943815410137177</v>
+        <v>0.005366108845919371</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.05418318137526512</v>
+        <v>0.003738434985280037</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.04225100949406624</v>
+        <v>0.00293104606680572</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.02653134986758232</v>
+        <v>0.001185010420158505</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0167052149772644</v>
+        <v>0.008666259236633778</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.4403688907623291</v>
+        <v>0.02297588065266609</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.04847679287195206</v>
+        <v>0.01770146563649178</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1540778279304504</v>
+        <v>0.01467202603816986</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.003858443349599838</v>
+        <v>0.03356356918811798</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.02797913551330566</v>
+        <v>0.02301433682441711</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.03628381341695786</v>
+        <v>0.005732719320803881</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.05223960801959038</v>
+        <v>0.002103199483826756</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.003428908064961433</v>
+        <v>0.008760819211602211</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.03768634051084518</v>
+        <v>0.01004479918628931</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.1348803490400314</v>
+        <v>0.003051575273275375</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.1136846542358398</v>
+        <v>0.01609672233462334</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.05407010018825531</v>
+        <v>0.004226377233862877</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.1065358966588974</v>
+        <v>0.01643625646829605</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.02506028115749359</v>
+        <v>0.006212965585291386</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.1261210739612579</v>
+        <v>0.0105148907750845</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.02969706617295742</v>
+        <v>0.001657474553212523</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.02777366526424885</v>
+        <v>0.005918656475841999</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.09287285059690475</v>
+        <v>0.001934539759531617</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.00533673632889986</v>
+        <v>0.002280252752825618</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0346105620265007</v>
+        <v>0.00278320861980319</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.01067779306322336</v>
+        <v>0.003024473320692778</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.04845386371016502</v>
+        <v>0.004036263562738895</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0522211454808712</v>
+        <v>0.003239192999899387</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.07697617262601852</v>
+        <v>0.000790090300142765</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.002440694719552994</v>
+        <v>0.003232791088521481</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.02851004712283611</v>
+        <v>0.001774775912053883</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.05163828283548355</v>
+        <v>0.005573826842010021</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.2527001202106476</v>
+        <v>0.01962130889296532</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0661969855427742</v>
+        <v>0.006972445175051689</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.05788062512874603</v>
+        <v>0.0210509579628706</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.04353641718626022</v>
+        <v>0.006325074471533298</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.03205588087439537</v>
+        <v>0.01305393129587173</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.001811079331673682</v>
+        <v>0.004552301950752735</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.04563008248806</v>
+        <v>0.001569269574247301</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.02421988360583782</v>
+        <v>0.004349611699581146</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.005160291213542223</v>
+        <v>0.004405246116220951</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1025051772594452</v>
+        <v>0.01731458865106106</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.01994222775101662</v>
+        <v>0.0007519798818975687</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0534914992749691</v>
+        <v>0.01053241826593876</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.005835083778947592</v>
+        <v>0.0003434745012782514</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.02152559161186218</v>
+        <v>0.007469493430107832</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.01402693334966898</v>
+        <v>0.0006400647689588368</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0118761258199811</v>
+        <v>0.003862999845296144</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.02043670788407326</v>
+        <v>0.002055266639217734</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.09124672412872314</v>
+        <v>0.009517624974250793</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.02562309801578522</v>
+        <v>0.006382779218256474</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0268031544983387</v>
+        <v>0.02550280466675758</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.08318665623664856</v>
+        <v>0.02212787047028542</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.1866361796855927</v>
+        <v>0.006408647634088993</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.003260659519582987</v>
+        <v>0.007495705969631672</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.02109350450336933</v>
+        <v>0.001983511727303267</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.1119547560811043</v>
+        <v>0.0007374502019956708</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.004198289941996336</v>
+        <v>0.0002522569557186216</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.01948396489024162</v>
+        <v>0.003916782326996326</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.1155065149068832</v>
+        <v>0.01625049859285355</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.03987625613808632</v>
+        <v>0.003521914128214121</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.06852103769779205</v>
+        <v>0.01087853498756886</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.02995042316615582</v>
+        <v>0.002692737383767962</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.03196481615304947</v>
+        <v>0.008233520202338696</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.006020398810505867</v>
+        <v>0.00122610991820693</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.001680255867540836</v>
+        <v>0.002917649690061808</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.009151315316557884</v>
+        <v>0.0008624818874523044</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1171762123703957</v>
+        <v>0.000510231708176434</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.07568230479955673</v>
+        <v>0.009835490956902504</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.019233213737607</v>
+        <v>0.0008270032703876495</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.3247711658477783</v>
+        <v>0.01092675793915987</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.004529107362031937</v>
+        <v>0.0111637394875288</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.03015310131013393</v>
+        <v>0.03258912265300751</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.03603024780750275</v>
+        <v>0.0003246745327487588</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.03576849028468132</v>
+        <v>0.01964034885168076</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.01156455650925636</v>
+        <v>0.005081838462501764</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.001725339330732822</v>
+        <v>0.004498156253248453</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.03086135536432266</v>
+        <v>0.008881454356014729</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.01501914765685797</v>
+        <v>0.0004168772138655186</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.05538095906376839</v>
+        <v>0.00229805801063776</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.1099287047982216</v>
+        <v>0.003282187972217798</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.03399689495563507</v>
+        <v>0.002242281567305326</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.01824294775724411</v>
+        <v>0.002412502188235521</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.02796095423400402</v>
+        <v>0.004999731667339802</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.03247235715389252</v>
+        <v>0.009171569719910622</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0170732568949461</v>
+        <v>0.0007093633757904172</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.1489705890417099</v>
+        <v>0.001833521877415478</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0238010473549366</v>
+        <v>0.01727907359600067</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.1051419600844383</v>
+        <v>0.003297199727967381</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.06900952756404877</v>
+        <v>0.001718207728117704</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.03711860999464989</v>
+        <v>0.01114817336201668</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.03952561691403389</v>
+        <v>0.0005404213443398476</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.01052683033049107</v>
+        <v>0.01827633194625378</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.01312089432030916</v>
+        <v>0.02471695095300674</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.011864323168993</v>
+        <v>0.01091158203780651</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.05292399600148201</v>
+        <v>0.009071394801139832</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.02869994007050991</v>
+        <v>0.01307810842990875</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.07049732655286789</v>
+        <v>0.01303804665803909</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.1052038073539734</v>
+        <v>0.002932955743744969</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.06033937633037567</v>
+        <v>0.00693031121045351</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.007711340673267841</v>
+        <v>0.0008186179911717772</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.001080021262168884</v>
+        <v>0.0001131815370172262</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.004505572840571404</v>
+        <v>0.00091557577252388</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.004070322029292583</v>
+        <v>0.003024218371137977</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.1023948490619659</v>
+        <v>0.0217038169503212</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.04034928604960442</v>
+        <v>0.002854081569239497</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.02663244307041168</v>
+        <v>0.01165064796805382</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.05108750239014626</v>
+        <v>0.008476453833281994</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.1416569650173187</v>
+        <v>0.0006668716087006032</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.02269160374999046</v>
+        <v>0.003204191103577614</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.008963095024228096</v>
+        <v>0.005604708101600409</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.003263238817453384</v>
+        <v>0.0005306212697178125</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.01568945683538914</v>
+        <v>0.003481720807030797</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.1138348877429962</v>
+        <v>0.01871638558804989</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.01007199753075838</v>
+        <v>0.001343058655038476</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.06512009352445602</v>
+        <v>0.01357422396540642</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.009699326939880848</v>
+        <v>0.001376051921397448</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.03510008007287979</v>
+        <v>0.00745259178802371</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.003413371508941054</v>
+        <v>0.001736382488161325</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.004007234238088131</v>
+        <v>0.003971136175096035</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.01841291785240173</v>
+        <v>0.002853131620213389</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.00144517794251442</v>
+        <v>0.002745202975347638</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.02829910255968571</v>
+        <v>0.005318771582096815</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.02069306746125221</v>
+        <v>0.0002531500067561865</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.03284269198775291</v>
+        <v>0.005106010474264622</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.03477334231138229</v>
+        <v>0.006254684180021286</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.02041473612189293</v>
+        <v>0.004184982273727655</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.06320461630821228</v>
+        <v>0.0008917137747630477</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.01311563514173031</v>
+        <v>0.003974361345171928</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.02496881783008575</v>
+        <v>0.006858913227915764</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.04180842265486717</v>
+        <v>0.00528246071189642</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.1173268631100655</v>
+        <v>0.01982628367841244</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.06503699719905853</v>
+        <v>0.007083956152200699</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0784282311797142</v>
+        <v>0.00994548387825489</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.1107351779937744</v>
+        <v>0.02534519881010056</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.06255938857793808</v>
+        <v>0.0006474200636148453</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.03646522387862206</v>
+        <v>0.00242452067323029</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.02184885554015636</v>
+        <v>0.01439918391406536</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.04669969156384468</v>
+        <v>0.01512821950018406</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.05239056050777435</v>
+        <v>0.003986886236816645</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.05475085228681564</v>
+        <v>0.003350182436406612</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.01343971118330956</v>
+        <v>0.004354153294116259</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.05520043522119522</v>
+        <v>0.01987279951572418</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.164999321103096</v>
+        <v>0.01650087162852287</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.1202185750007629</v>
+        <v>0.01293865498155355</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.1145270168781281</v>
+        <v>0.008450974710285664</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.02679888717830181</v>
+        <v>0.002045581350103021</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.01232378929853439</v>
+        <v>0.006719187833368778</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.02135307341814041</v>
+        <v>0.001205364242196083</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00273378100246191</v>
+        <v>0.001539074350148439</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005203518085181713</v>
+        <v>0.001823455095291138</v>
       </c>
       <c r="D6" t="n">
-        <v>0.009204348549246788</v>
+        <v>0.009559032507240772</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01286322250962257</v>
+        <v>0.001435434329323471</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004718712531030178</v>
+        <v>1.926043478306383e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003455574158579111</v>
+        <v>0.003115513594821095</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004013543017208576</v>
+        <v>0.00125962367746979</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00272669643163681</v>
+        <v>0.0001838607713580132</v>
       </c>
       <c r="J6" t="n">
-        <v>0.01939456537365913</v>
+        <v>0.001096369582228363</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001979356165975332</v>
+        <v>0.0003777725505642593</v>
       </c>
       <c r="L6" t="n">
-        <v>0.005135166458785534</v>
+        <v>0.001126911723986268</v>
       </c>
       <c r="M6" t="n">
-        <v>0.004677275661379099</v>
+        <v>0.01249224692583084</v>
       </c>
       <c r="N6" t="n">
-        <v>0.005261313635855913</v>
+        <v>0.001120814005844295</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0005614231922663748</v>
+        <v>0.002066405722871423</v>
       </c>
       <c r="P6" t="n">
-        <v>0.002966535277664661</v>
+        <v>0.003599172225221992</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001818679040297866</v>
+        <v>0.0008119559497572482</v>
       </c>
       <c r="R6" t="n">
-        <v>0.006388742942363024</v>
+        <v>0.0004501657676883042</v>
       </c>
       <c r="S6" t="n">
-        <v>0.00373563077300787</v>
+        <v>0.0003374645602889359</v>
       </c>
       <c r="T6" t="n">
-        <v>0.00604701042175293</v>
+        <v>0.0001765515771694481</v>
       </c>
       <c r="U6" t="n">
-        <v>0.002126209903508425</v>
+        <v>0.000264830538071692</v>
       </c>
       <c r="V6" t="n">
-        <v>0.004443763755261898</v>
+        <v>0.0009183381916955113</v>
       </c>
       <c r="W6" t="n">
-        <v>0.005180827341973782</v>
+        <v>0.0009797640377655625</v>
       </c>
       <c r="X6" t="n">
-        <v>0.001691665849648416</v>
+        <v>0.0007334070978686213</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.001036089030094445</v>
+        <v>0.000421862379880622</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.005764576606452465</v>
+        <v>0.0005532262148335576</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0002363971580052748</v>
+        <v>0.0002609122893773019</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.001033233013004065</v>
+        <v>0.0006428636843338609</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0108862342312932</v>
+        <v>0.001484545180574059</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0001296231057494879</v>
+        <v>0.0002550789504311979</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.003210231196135283</v>
+        <v>0.0002534269879106432</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.003186509013175964</v>
+        <v>0.0005976264365017414</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.965549593791366e-05</v>
+        <v>0.001238832366652787</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0001706538896542042</v>
+        <v>0.0008251193212345243</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0009645855752751231</v>
+        <v>0.0008234101114794612</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.003271439345553517</v>
+        <v>0.001871081651188433</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0002615222474560142</v>
+        <v>0.0003469517105259001</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.002618193859234452</v>
+        <v>0.00110866385512054</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.002905047032982111</v>
+        <v>4.25113394157961e-05</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.00122801773250103</v>
+        <v>0.001726881950162351</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.002089006127789617</v>
+        <v>3.525968713802285e-05</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.002714159432798624</v>
+        <v>0.0005105333984829485</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.001236278214491904</v>
+        <v>0.001777078025043011</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.003547369036823511</v>
+        <v>0.0001838891621446237</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0007039819029159844</v>
+        <v>8.450380119029433e-05</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.01110354159027338</v>
+        <v>7.17712682671845e-05</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.006285130046308041</v>
+        <v>0.0006167601677589118</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.004292591940611601</v>
+        <v>0.0005540120182558894</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.003098469693213701</v>
+        <v>0.005227395333349705</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.01037085242569447</v>
+        <v>0.004425153601914644</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0003080841852352023</v>
+        <v>0.0004240109992679209</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.005089857149869204</v>
+        <v>1.48814870044589e-05</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.005217554047703743</v>
+        <v>0.001068897312507033</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.001734561985358596</v>
+        <v>0.00107525335624814</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.01153348013758659</v>
+        <v>0.001802372396923602</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.01218937896192074</v>
+        <v>5.36709267180413e-05</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.728270091116428e-05</v>
+        <v>0.001013489672914147</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0002820300869643688</v>
+        <v>0.000495826592668891</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.003170715644955635</v>
+        <v>0.002148420549929142</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0009556742152199149</v>
+        <v>0.0007370023522526026</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0006650252616964281</v>
+        <v>0.001360278343781829</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.004034774843603373</v>
+        <v>0.001590027357451618</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.007543481886386871</v>
+        <v>0.002570072887465358</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.001216295757330954</v>
+        <v>0.0004395650466904044</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.00431041419506073</v>
+        <v>0.0001839149772422388</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0003979155444540083</v>
+        <v>0.0002885881694965065</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.003861074801534414</v>
+        <v>0.001702680485323071</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.005417169071733952</v>
+        <v>0.002262545982375741</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.002786835422739387</v>
+        <v>0.0006062060128897429</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0003781707782763988</v>
+        <v>0.0006259851506911218</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.003167630173265934</v>
+        <v>0.0003999565378762782</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.004052743315696716</v>
+        <v>0.0005779053899459541</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.005719667766243219</v>
+        <v>2.68783769570291e-05</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0005545049789361656</v>
+        <v>5.72793487663148e-06</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0006117256125435233</v>
+        <v>0.0002334813761990517</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.0008052857010625303</v>
+        <v>0.00459687877446413</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.007863347418606281</v>
+        <v>0.001979636494070292</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.001317655784077942</v>
+        <v>0.001062686322256923</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.003565886057913303</v>
+        <v>0.000511509133502841</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.004232027102261782</v>
+        <v>0.0001574040798004717</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.002122335368767381</v>
+        <v>0.0004752125823870301</v>
       </c>
       <c r="CD6" t="n">
-        <v>0.003510735929012299</v>
+        <v>0.0003745644353330135</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.003654442494735122</v>
+        <v>0.0008610875229351223</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.0004843161441385746</v>
+        <v>0.0001041015420923941</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0007258565165102482</v>
+        <v>0.003386775497347116</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.002657473320141435</v>
+        <v>0.0001170232571894303</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.004404411651194096</v>
+        <v>0.0009252927848137915</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.001229611225426197</v>
+        <v>7.552240276709199e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.002908861264586449</v>
+        <v>0.000909622700419277</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.001571605680510402</v>
+        <v>0.0001800498284865171</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.006455798167735338</v>
+        <v>0.0003062395262531936</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.003077555447816849</v>
+        <v>0.0004927993286401033</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.001400112407281995</v>
+        <v>0.001207427703775465</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.007396957371383905</v>
+        <v>0.005026437807828188</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.008202484808862209</v>
+        <v>0.003231866750866175</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.005545771680772305</v>
+        <v>0.00159362843260169</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.002361305058002472</v>
+        <v>0.0002931163471657783</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.005189941264688969</v>
+        <v>0.001583400066010654</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.002073446754366159</v>
+        <v>0.001765139983035624</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.002623458858579397</v>
+        <v>0.0002598954597488046</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.003827937645837665</v>
+        <v>0.0008088186150416732</v>
       </c>
       <c r="CX6" t="n">
-        <v>0.00100096850655973</v>
+        <v>3.101537004113197e-05</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.79946146090515e-05</v>
+        <v>0.003734659403562546</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.002567540388554335</v>
+        <v>0.000261676759691909</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.003839259967207909</v>
+        <v>0.0005818710196763277</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.001052533043548465</v>
+        <v>0.0003020744188688695</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.00237658154219389</v>
+        <v>0.0007687185425311327</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.001781214727088809</v>
+        <v>8.616416016593575e-05</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.003578370437026024</v>
+        <v>1.674797385931015e-05</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.006207214668393135</v>
+        <v>0.001354254083707929</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.004914905875921249</v>
+        <v>0.0003533023118507117</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.002238129964098334</v>
+        <v>0.002048151567578316</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.004285837057977915</v>
+        <v>0.0003303321427665651</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.006290137767791748</v>
+        <v>0.001213885494507849</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0006431769579648972</v>
+        <v>0.0006249911384657025</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.007951728999614716</v>
+        <v>0.00361786293797195</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0001703617163002491</v>
+        <v>0.0005851557943969965</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.00303354999050498</v>
+        <v>0.0002856064238585532</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0001105577684938908</v>
+        <v>0.001053381361998618</v>
       </c>
       <c r="DP6" t="n">
-        <v>0.0009761821711435914</v>
+        <v>0.001405696268193424</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.005593471694737673</v>
+        <v>0.001564648817293346</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.005152836441993713</v>
+        <v>0.0003576776653062552</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.001849364256486297</v>
+        <v>0.001269776606932282</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.0005469723255373538</v>
+        <v>0.0009632562869228423</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.001665584277361631</v>
+        <v>0.0008820979855954647</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.001984312664717436</v>
+        <v>0.002398341195657849</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.004561977460980415</v>
+        <v>0.0001661350252106786</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.002239260822534561</v>
+        <v>0.00029221479780972</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.002888958435505629</v>
+        <v>0.003252691123634577</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0007739351713098586</v>
+        <v>0.0009623855585232377</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0001370137324556708</v>
+        <v>0.000343983992934227</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.003454138059169054</v>
+        <v>0.001133040292188525</v>
       </c>
       <c r="EC6" t="n">
-        <v>0.003228500718250871</v>
+        <v>0.0005831199232488871</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.002287312177941203</v>
+        <v>0.003369786776602268</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.001144691021181643</v>
+        <v>0.001781988306902349</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.00417865626513958</v>
+        <v>0.001970877405256033</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.006514056120067835</v>
+        <v>0.0002844971604645252</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.004886126611381769</v>
+        <v>0.0002973897499032319</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.002443953882902861</v>
+        <v>0.003565731924027205</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.000735971552785486</v>
+        <v>0.0003210569848306477</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.002536620246246457</v>
+        <v>0.0008529186598025262</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.001067901961505413</v>
+        <v>6.040270091034472e-05</v>
       </c>
       <c r="EM6" t="n">
-        <v>0.002484249416738749</v>
+        <v>0.000367068947525695</v>
       </c>
       <c r="EN6" t="n">
-        <v>0.0002373834868194535</v>
+        <v>0.0001240509445779026</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0001310299849137664</v>
+        <v>0.0004969752626493573</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.008232827298343182</v>
+        <v>0.001679043401964009</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.000861309701576829</v>
+        <v>0.00107654626481235</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.001798117649741471</v>
+        <v>0.003102464601397514</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.0007598076481372118</v>
+        <v>8.279179382952861e-06</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.003717696294188499</v>
+        <v>0.001918163266964257</v>
       </c>
       <c r="EU6" t="n">
-        <v>4.833878483623266e-05</v>
+        <v>0.001166862319223583</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.00480000302195549</v>
+        <v>0.0009940586751326919</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.006594681646674871</v>
+        <v>0.001614535809494555</v>
       </c>
       <c r="EX6" t="n">
-        <v>0.003131368663161993</v>
+        <v>0.0002459973329678178</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.004017812199890614</v>
+        <v>0.0006327229784801602</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0007970464648678899</v>
+        <v>0.0003676597261801362</v>
       </c>
       <c r="FA6" t="n">
-        <v>4.528513818513602e-05</v>
+        <v>0.003958793357014656</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.002729491563513875</v>
+        <v>0.0001715601538307965</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.002979060402140021</v>
+        <v>0.0003545068029779941</v>
       </c>
       <c r="FD6" t="n">
-        <v>0.0007960842922329903</v>
+        <v>0.0002663253399077803</v>
       </c>
       <c r="FE6" t="n">
-        <v>0.002830215496942401</v>
+        <v>0.00103846681304276</v>
       </c>
       <c r="FF6" t="n">
-        <v>0.001575177768245339</v>
+        <v>4.474811430554837e-05</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.002424118109047413</v>
+        <v>0.0002473657950758934</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.002174183027818799</v>
+        <v>0.000368914712453261</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.003624174045398831</v>
+        <v>0.0007592716719955206</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.001211904571391642</v>
+        <v>0.001600456889718771</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.003933961037546396</v>
+        <v>0.001057015731930733</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.002770709106698632</v>
+        <v>0.001398171065375209</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.003132743295282125</v>
+        <v>0.000233135127928108</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0004652774077840149</v>
+        <v>0.0009009458008222282</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.001939987996593118</v>
+        <v>0.000504185154568404</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.003644388634711504</v>
+        <v>0.001673792372457683</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.003726673312485218</v>
+        <v>0.003317943075671792</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.007485599257051945</v>
+        <v>0.0001158484374172986</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0002440958342049271</v>
+        <v>0.002563046058639884</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.01164679881185293</v>
+        <v>0.0007308844942599535</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.002154979389160872</v>
+        <v>0.001803437829948962</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.003348408034071326</v>
+        <v>0.0001057546469382942</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.001908631063997746</v>
+        <v>0.002586499089375138</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.000105727172922343</v>
+        <v>0.0008991198264993727</v>
       </c>
       <c r="FY6" t="n">
-        <v>0.00157058541662991</v>
+        <v>0.000668682623654604</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.002360031241551042</v>
+        <v>0.0007711736252531409</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.002769218292087317</v>
+        <v>0.0009258940117433667</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.00169346434995532</v>
+        <v>0.002769507467746735</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0009393293294124305</v>
+        <v>0.001044370350427926</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.001496126409620047</v>
+        <v>0.001093094469979405</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.005745168309658766</v>
+        <v>0.002224860712885857</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.001711607445031404</v>
+        <v>0.0004000177141278982</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.002279964974150062</v>
+        <v>0.0003139346372336149</v>
       </c>
     </row>
     <row r="7">
@@ -4982,3985 +4982,3985 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0003971841069869697</v>
+        <v>1.295944684898132e-08</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001710101496428251</v>
+        <v>4.235701567267824e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0002859951055143028</v>
+        <v>5.24134380341934e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001072206767275929</v>
+        <v>2.245452002114234e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0005993124796077609</v>
+        <v>1.699846485792023e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0004722950397990644</v>
+        <v>3.00326696844877e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001733827230054885</v>
+        <v>1.39213551797468e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>5.893967681913637e-05</v>
+        <v>4.320971580540345e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.688340413849801e-05</v>
+        <v>5.038670369827969e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000627560424618423</v>
+        <v>1.290715312407542e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001282758079469204</v>
+        <v>4.28820996489776e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002463397104293108</v>
+        <v>8.975382215226091e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0007160618552006781</v>
+        <v>3.690863792371601e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0007236567907966673</v>
+        <v>1.822021467035029e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0008595254039391875</v>
+        <v>2.956854139313236e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>0.000249348406214267</v>
+        <v>6.387895989945491e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.000379653210984543</v>
+        <v>1.010823869052047e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0001850329572334886</v>
+        <v>3.666549730496627e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>1.400527253281325e-06</v>
+        <v>5.076277176385702e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0003166136448271573</v>
+        <v>5.036065342522988e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0001563186233397573</v>
+        <v>1.162907103946509e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0001153462508227676</v>
+        <v>3.325895114869581e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>0.000291600328637287</v>
+        <v>7.039371308081854e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0002425952989142388</v>
+        <v>7.52941886617009e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0003255065821576864</v>
+        <v>1.32169892808065e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.000144768797326833</v>
+        <v>7.504995735985176e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0002951955830212682</v>
+        <v>2.176103741646784e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.605472637806088e-05</v>
+        <v>2.749928285084025e-09</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0001269220520043746</v>
+        <v>8.615553603874559e-09</v>
       </c>
       <c r="AD9" t="n">
-        <v>9.438856795895845e-05</v>
+        <v>2.741814997264669e-09</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0001320886221947148</v>
+        <v>1.326383003430465e-08</v>
       </c>
       <c r="AF9" t="n">
-        <v>7.855888543417677e-05</v>
+        <v>5.710909078970872e-09</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.001663521397859e-05</v>
+        <v>1.570805530093367e-08</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0001441935601178557</v>
+        <v>1.42248535173195e-09</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.201611202210188e-06</v>
+        <v>1.511485514527067e-08</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.061186387436464e-05</v>
+        <v>3.757776312340866e-09</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0002631943207234144</v>
+        <v>5.255536450476939e-09</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0001793349656509236</v>
+        <v>5.102875899609671e-09</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0001144306879723445</v>
+        <v>1.715427799808822e-08</v>
       </c>
       <c r="AN9" t="n">
-        <v>6.156248855404556e-05</v>
+        <v>8.727942812924994e-09</v>
       </c>
       <c r="AO9" t="n">
-        <v>5.437430445454083e-05</v>
+        <v>4.614034487815388e-09</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.647092514962424e-05</v>
+        <v>9.659474109469102e-09</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0001116001221816987</v>
+        <v>4.1947814111154e-09</v>
       </c>
       <c r="AR9" t="n">
-        <v>8.325357339344919e-05</v>
+        <v>2.12380957265168e-09</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0001768356014508754</v>
+        <v>3.875413323584098e-09</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.47961236507399e-05</v>
+        <v>2.476903349091231e-09</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.001067715929821134</v>
+        <v>2.621305483785363e-08</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.314980520168319e-05</v>
+        <v>2.291280765120973e-08</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0002228681405540556</v>
+        <v>5.41721778546389e-09</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.215062164003029e-05</v>
+        <v>4.226690819564283e-08</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0001542707905173302</v>
+        <v>3.119572156151662e-08</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6.810895138187334e-05</v>
+        <v>2.320375669384589e-09</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0002388044667895883</v>
+        <v>9.035967529769096e-09</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0002748802944552153</v>
+        <v>1.869429056000627e-10</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0002457255031913519</v>
+        <v>4.043599677316934e-09</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0002983928425237536</v>
+        <v>1.638292346228809e-08</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0005465077119879425</v>
+        <v>1.737259225365051e-09</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0002229693491244689</v>
+        <v>1.656844084152453e-08</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0005896176444366574</v>
+        <v>2.867443349430232e-08</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.0002808005956467241</v>
+        <v>4.388281737988109e-09</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.682171493186615e-06</v>
+        <v>5.330262453639989e-09</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0003520766622386873</v>
+        <v>1.473708532984119e-08</v>
       </c>
       <c r="BK9" t="n">
-        <v>4.245291347615421e-05</v>
+        <v>3.601800413477463e-09</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.000221159280044958</v>
+        <v>3.148912686157246e-09</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0002646750072017312</v>
+        <v>3.849524254917469e-09</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0002783612872008234</v>
+        <v>2.385826203266106e-09</v>
       </c>
       <c r="BO9" t="n">
-        <v>8.999909914564341e-05</v>
+        <v>5.865234520285867e-09</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0001892338768811896</v>
+        <v>1.453837228382326e-08</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.762535485904664e-05</v>
+        <v>1.154687456761394e-09</v>
       </c>
       <c r="BR9" t="n">
-        <v>8.010011515580118e-05</v>
+        <v>1.564155693856151e-09</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0002448115847073495</v>
+        <v>6.894715909311344e-09</v>
       </c>
       <c r="BT9" t="n">
-        <v>1.935546606546268e-06</v>
+        <v>3.670912462894194e-09</v>
       </c>
       <c r="BU9" t="n">
-        <v>9.278868674300611e-05</v>
+        <v>3.021459971108698e-09</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.0004878632607869804</v>
+        <v>1.019258455414729e-08</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0003327725280541927</v>
+        <v>1.262911197841277e-08</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.0001223956060130149</v>
+        <v>2.556458156277586e-09</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.974093513330445e-05</v>
+        <v>5.221801657739888e-09</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.01091354736127e-05</v>
+        <v>1.523148362991833e-08</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.000240405322983861</v>
+        <v>1.064895105429287e-08</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.067929355893284e-05</v>
+        <v>1.136995830819387e-09</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0001466694957343861</v>
+        <v>4.782589324570097e-10</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.604468681965955e-05</v>
+        <v>1.785205427928815e-09</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0002931218768935651</v>
+        <v>1.504487379122565e-08</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0002209216327173635</v>
+        <v>4.728091251848809e-10</v>
       </c>
       <c r="CG9" t="n">
-        <v>6.143379141576588e-05</v>
+        <v>7.704413107489927e-09</v>
       </c>
       <c r="CH9" t="n">
-        <v>6.116322765592486e-05</v>
+        <v>3.148689753373901e-09</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0001299337454838678</v>
+        <v>5.86688519987888e-09</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.638578396523371e-05</v>
+        <v>4.202256320695597e-09</v>
       </c>
       <c r="CK9" t="n">
-        <v>2.127553671016358e-05</v>
+        <v>1.036572161439153e-09</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0001919068745337427</v>
+        <v>3.580474139397438e-09</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0001722957531455904</v>
+        <v>1.014097694707061e-08</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.7859238141682e-05</v>
+        <v>2.139966426284445e-08</v>
       </c>
       <c r="CO9" t="n">
-        <v>7.633874338353053e-05</v>
+        <v>2.131612930611482e-08</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0004521671507973224</v>
+        <v>1.227951784699144e-08</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.000325998873449862</v>
+        <v>1.09402009673687e-09</v>
       </c>
       <c r="CR9" t="n">
-        <v>7.998375076567754e-05</v>
+        <v>1.138630967290055e-09</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0003026896738447249</v>
+        <v>4.670161590780708e-09</v>
       </c>
       <c r="CT9" t="n">
-        <v>4.236546010361053e-05</v>
+        <v>9.655798827168383e-09</v>
       </c>
       <c r="CU9" t="n">
-        <v>7.064070086926222e-05</v>
+        <v>4.7554573612274e-09</v>
       </c>
       <c r="CV9" t="n">
-        <v>5.990649242448853e-06</v>
+        <v>3.169340123676534e-09</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0002608841750770807</v>
+        <v>1.412634809128122e-08</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.0001956149062607437</v>
+        <v>9.966957259521791e-10</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0001716073311399668</v>
+        <v>9.213110274686187e-09</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0001064395619323477</v>
+        <v>5.459397822704659e-09</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0001498486672062427</v>
+        <v>6.344871295027588e-09</v>
       </c>
       <c r="DB9" t="n">
-        <v>6.076984573155642e-05</v>
+        <v>4.854117996444529e-09</v>
       </c>
       <c r="DC9" t="n">
-        <v>5.290300396154635e-05</v>
+        <v>1.202467125871465e-09</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0001594641653355211</v>
+        <v>2.627946082967014e-09</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0002365819382248446</v>
+        <v>5.925001378415118e-09</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0001135752681875601</v>
+        <v>2.163114798392485e-09</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.000372385693481192</v>
+        <v>1.454658615784865e-09</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0008267290540970862</v>
+        <v>2.649280350652816e-09</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0005475540529005229</v>
+        <v>5.636594746505352e-09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0001333089603576809</v>
+        <v>1.534452920282092e-08</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0001256820105481893</v>
+        <v>2.896501705151877e-09</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0001904152595670894</v>
+        <v>1.281713046807909e-08</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0001013453293126076</v>
+        <v>2.236134166722081e-09</v>
       </c>
       <c r="DN9" t="n">
-        <v>4.849714241572656e-05</v>
+        <v>2.262065645908251e-09</v>
       </c>
       <c r="DO9" t="n">
-        <v>9.954523557098582e-05</v>
+        <v>5.861554797093049e-09</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0001767940848367289</v>
+        <v>4.187603597216594e-10</v>
       </c>
       <c r="DQ9" t="n">
-        <v>8.045151480473578e-05</v>
+        <v>8.216221480950026e-09</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.00438753888011e-05</v>
+        <v>7.433095805531309e-10</v>
       </c>
       <c r="DS9" t="n">
-        <v>6.886946357553825e-05</v>
+        <v>2.885514494010977e-09</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.0001135666243499145</v>
+        <v>1.018998130319915e-08</v>
       </c>
       <c r="DU9" t="n">
-        <v>4.360463208286092e-06</v>
+        <v>7.88546117291844e-09</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0003345553705003113</v>
+        <v>1.625989232145741e-09</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.0001925542019307613</v>
+        <v>7.17264303506937e-10</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0001408574171364307</v>
+        <v>3.536362758183031e-09</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0003598491020966321</v>
+        <v>9.522690191943184e-09</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2.935437623818871e-05</v>
+        <v>6.947557196212983e-09</v>
       </c>
       <c r="EA9" t="n">
-        <v>3.287077561253682e-05</v>
+        <v>1.060905407967994e-08</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.0003166843089275062</v>
+        <v>2.127265030793524e-09</v>
       </c>
       <c r="EC9" t="n">
-        <v>8.528029866283759e-05</v>
+        <v>5.513522971511975e-09</v>
       </c>
       <c r="ED9" t="n">
-        <v>2.471273000992369e-05</v>
+        <v>1.636284885364603e-08</v>
       </c>
       <c r="EE9" t="n">
-        <v>1.793795854609925e-05</v>
+        <v>1.019777773336727e-08</v>
       </c>
       <c r="EF9" t="n">
-        <v>8.041026012506336e-05</v>
+        <v>2.957431632921725e-09</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0002340383070986718</v>
+        <v>6.346470016183048e-09</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0001198294994537719</v>
+        <v>7.379383326622246e-09</v>
       </c>
       <c r="EI9" t="n">
-        <v>4.417351374286227e-05</v>
+        <v>6.469562663369288e-09</v>
       </c>
       <c r="EJ9" t="n">
-        <v>9.228406270267442e-05</v>
+        <v>5.005627912169075e-09</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0001084586547221988</v>
+        <v>4.955998722522281e-09</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001225051819346845</v>
+        <v>6.363453763924554e-09</v>
       </c>
       <c r="EM9" t="n">
-        <v>8.219609298976138e-06</v>
+        <v>9.623191132845932e-10</v>
       </c>
       <c r="EN9" t="n">
-        <v>8.258161687990651e-05</v>
+        <v>3.611616561371989e-10</v>
       </c>
       <c r="EO9" t="n">
-        <v>2.404662882327102e-05</v>
+        <v>2.472581694945575e-09</v>
       </c>
       <c r="EP9" t="n">
-        <v>1.465003606426762e-05</v>
+        <v>8.226310299619399e-09</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0002279765903949738</v>
+        <v>3.372027990167226e-09</v>
       </c>
       <c r="ER9" t="n">
-        <v>8.073318895185366e-06</v>
+        <v>2.782133412537746e-09</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0001097971544368193</v>
+        <v>4.227038274962069e-09</v>
       </c>
       <c r="ET9" t="n">
-        <v>9.794379002414644e-05</v>
+        <v>6.280056474849971e-10</v>
       </c>
       <c r="EU9" t="n">
-        <v>4.055554018123075e-05</v>
+        <v>1.178697361936543e-09</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0004453625879250467</v>
+        <v>6.623093629087862e-09</v>
       </c>
       <c r="EW9" t="n">
-        <v>7.639155955985188e-05</v>
+        <v>5.268743663577879e-09</v>
       </c>
       <c r="EX9" t="n">
-        <v>2.398557626293041e-05</v>
+        <v>1.722571529860772e-09</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0002457978844176978</v>
+        <v>1.579366681880856e-08</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0001642513234401122</v>
+        <v>1.259057746949566e-09</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0001004435544018634</v>
+        <v>9.393754218933736e-09</v>
       </c>
       <c r="FB9" t="n">
-        <v>6.816013774368912e-05</v>
+        <v>6.478722558433958e-10</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0001293407258344814</v>
+        <v>3.693630512557888e-09</v>
       </c>
       <c r="FD9" t="n">
-        <v>7.059668132569641e-05</v>
+        <v>2.450312841517643e-09</v>
       </c>
       <c r="FE9" t="n">
-        <v>3.698321961564943e-06</v>
+        <v>2.394073828071441e-09</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0002305599773535505</v>
+        <v>3.79613201983986e-10</v>
       </c>
       <c r="FG9" t="n">
-        <v>0.0001638541143620387</v>
+        <v>1.146380101957334e-09</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0001049728089128621</v>
+        <v>9.858149851993403e-09</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.000340104685164988</v>
+        <v>4.30327329326019e-09</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0003186904650647193</v>
+        <v>7.433741622264733e-09</v>
       </c>
       <c r="FK9" t="n">
-        <v>2.761498399195261e-05</v>
+        <v>3.138303394933928e-09</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0002443192643113434</v>
+        <v>4.585451574001809e-09</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0001142751279985532</v>
+        <v>4.330689584719494e-09</v>
       </c>
       <c r="FN9" t="n">
-        <v>0.0003886179765686393</v>
+        <v>5.312830619885744e-09</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0002465664292685688</v>
+        <v>1.589927478562458e-08</v>
       </c>
       <c r="FP9" t="n">
-        <v>1.829729444580153e-05</v>
+        <v>2.008254007535015e-09</v>
       </c>
       <c r="FQ9" t="n">
-        <v>9.082623000722378e-05</v>
+        <v>2.190250647515768e-08</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0001170531468233094</v>
+        <v>1.291794582414241e-08</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.000149627318023704</v>
+        <v>3.598796816106642e-09</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0004604405839927495</v>
+        <v>2.325871051311879e-08</v>
       </c>
       <c r="FU9" t="n">
-        <v>5.471482290886343e-05</v>
+        <v>9.411762036393156e-09</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0001482782099628821</v>
+        <v>8.260588657549306e-09</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0003256094641983509</v>
+        <v>4.953981225241932e-09</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0001640051486901939</v>
+        <v>3.318367802762623e-09</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.000481984403450042</v>
+        <v>1.375712321838307e-09</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0001841447228798643</v>
+        <v>6.845997102544743e-10</v>
       </c>
       <c r="GA9" t="n">
-        <v>1.986224378924817e-05</v>
+        <v>1.232560897790336e-08</v>
       </c>
       <c r="GB9" t="n">
-        <v>7.448482210747898e-05</v>
+        <v>5.856575224783001e-09</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0004234908265061677</v>
+        <v>1.236354663092243e-08</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.000213589912164025</v>
+        <v>1.716276898378055e-08</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.0005576986586675048</v>
+        <v>1.332182630875423e-08</v>
       </c>
       <c r="GF9" t="n">
-        <v>4.324636756791733e-05</v>
+        <v>2.746218363824937e-09</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0001968022988876328</v>
+        <v>4.527151986621902e-09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.481365274637938e-05</v>
+        <v>3.066567453528096e-13</v>
       </c>
       <c r="B10" t="n">
-        <v>0.01553434040397406</v>
+        <v>1.022002849102727e-13</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0004273528466001153</v>
+        <v>5.723001147419846e-14</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00607116986066103</v>
+        <v>1.722815141415313e-13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003693130798637867</v>
+        <v>6.8690224949014e-14</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01019144244492054</v>
+        <v>7.5340192526481e-15</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0003842145088128746</v>
+        <v>3.085643719702436e-13</v>
       </c>
       <c r="H10" t="n">
-        <v>0.004018542356789112</v>
+        <v>1.707072661396095e-13</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002200609771534801</v>
+        <v>1.170261262027628e-13</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001836856827139854</v>
+        <v>2.333639737613774e-13</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01539464853703976</v>
+        <v>2.460623393409078e-13</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0005876834038645029</v>
+        <v>1.649171522000864e-13</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00462609063833952</v>
+        <v>4.072080400738948e-13</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0009553561685606837</v>
+        <v>2.632250428909189e-14</v>
       </c>
       <c r="O10" t="n">
-        <v>0.008601617999374866</v>
+        <v>6.356467273111593e-14</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0004994400078430772</v>
+        <v>9.140732333372259e-14</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.001036125002428889</v>
+        <v>3.349582980774479e-13</v>
       </c>
       <c r="R10" t="n">
-        <v>0.002069848356768489</v>
+        <v>4.793324889567838e-14</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0008321593049913645</v>
+        <v>2.194317590045042e-13</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0009949838276952505</v>
+        <v>2.394756214076782e-13</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0003344097349327058</v>
+        <v>7.643012741795352e-14</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0009101681644096971</v>
+        <v>6.298116189814781e-14</v>
       </c>
       <c r="W10" t="n">
-        <v>0.002083119936287403</v>
+        <v>1.500415528041428e-15</v>
       </c>
       <c r="X10" t="n">
-        <v>0.00107097125146538</v>
+        <v>1.553362744422665e-13</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0003398765111342072</v>
+        <v>1.559852168763441e-14</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.00173479353543371</v>
+        <v>1.305688413291706e-13</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.001449538394808769</v>
+        <v>2.398037280901266e-13</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0009878423297777772</v>
+        <v>2.000135625700172e-13</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0005076482193544507</v>
+        <v>1.22501469146559e-13</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0005702865892089903</v>
+        <v>1.767324622151817e-13</v>
       </c>
       <c r="AE10" t="n">
-        <v>5.076021625427529e-05</v>
+        <v>1.736843768850374e-13</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.001581199467182159</v>
+        <v>1.451595327229757e-13</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0009274390758946538</v>
+        <v>1.956437941340317e-13</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0004845790099352598</v>
+        <v>5.396093524811553e-14</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.001543031889013946</v>
+        <v>1.644399406138669e-13</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.887338632717729e-05</v>
+        <v>3.329976539737795e-14</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.001308077480643988</v>
+        <v>1.640631261488196e-13</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.001830694149248302</v>
+        <v>3.877029041777016e-14</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.001484203618019819</v>
+        <v>1.706372673368484e-13</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.005673928186297e-05</v>
+        <v>1.345185051402405e-14</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0002309621195308864</v>
+        <v>1.677256288501114e-13</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.001227257773280144</v>
+        <v>6.057707910593277e-14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0002983266313094646</v>
+        <v>3.440190433955451e-14</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0007172867190092802</v>
+        <v>3.278005037549159e-13</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0009520353050902486</v>
+        <v>4.334775472055429e-14</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.001631582155823708</v>
+        <v>2.963987833382725e-14</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.01000133529305458</v>
+        <v>4.10554755339923e-13</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.001321117859333754</v>
+        <v>2.177742984858441e-13</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0004247993638273329</v>
+        <v>3.706080852362154e-15</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0008819708018563688</v>
+        <v>6.854098451997137e-14</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.004731856286525726</v>
+        <v>5.279276161737102e-14</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.001718937419354916</v>
+        <v>1.418930484177114e-13</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.001125485519878566</v>
+        <v>1.618431408854926e-13</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.001185551518574357</v>
+        <v>3.721158716449638e-14</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.0001742715248838067</v>
+        <v>7.298522680318498e-13</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.003844282124191523</v>
+        <v>3.790152599322111e-13</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.002349536865949631</v>
+        <v>2.525739220635842e-13</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0004831818223465234</v>
+        <v>1.87584323074752e-13</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.00441645784303546</v>
+        <v>3.878143737135603e-13</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.003586122766137123</v>
+        <v>1.685650859346854e-13</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0003764114226214588</v>
+        <v>6.741226907204176e-14</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0004432670539245009</v>
+        <v>1.780758158119455e-13</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.001075640087947249</v>
+        <v>4.040434978778984e-13</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.001324971322901547</v>
+        <v>6.755023379849054e-14</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.002751813502982259</v>
+        <v>6.979800174248749e-14</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.001123911468312144</v>
+        <v>5.963139053724587e-14</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0006033631507307291</v>
+        <v>2.833296748258607e-13</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.001097792061045766</v>
+        <v>8.501276668303887e-15</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.0008324770024046302</v>
+        <v>1.53757540553856e-13</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0011703846976161</v>
+        <v>1.129442879824714e-13</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.0006550935213454068</v>
+        <v>7.44300725653152e-14</v>
       </c>
       <c r="BT10" t="n">
-        <v>3.339082468301058e-07</v>
+        <v>1.215180706710603e-13</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0009700702503323555</v>
+        <v>3.876789839672712e-13</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.005996468011289835</v>
+        <v>3.041750336850446e-13</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.0004600344691425562</v>
+        <v>2.514961437889707e-14</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0004280615830793977</v>
+        <v>1.625838407046803e-13</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0001320869487244636</v>
+        <v>6.668602302306592e-15</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.001975079067051411</v>
+        <v>1.085052186988733e-13</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0003669284633360803</v>
+        <v>3.696944754993069e-14</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0001983849506359547</v>
+        <v>9.701126620770273e-14</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.001369892619550228</v>
+        <v>1.336048513576188e-13</v>
       </c>
       <c r="CD10" t="n">
-        <v>7.840123726055026e-05</v>
+        <v>4.434278465248465e-15</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.002595968777313828</v>
+        <v>6.64024296160616e-14</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.000809486024081707</v>
+        <v>1.560854208740043e-14</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.000950013636611402</v>
+        <v>5.043574336383722e-14</v>
       </c>
       <c r="CH10" t="n">
-        <v>4.902176442556083e-05</v>
+        <v>7.850449077698857e-14</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.00168975442647934</v>
+        <v>5.315904238068631e-15</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.001230225898325443</v>
+        <v>1.164262879627034e-14</v>
       </c>
       <c r="CK10" t="n">
-        <v>5.207054346101359e-05</v>
+        <v>3.046734143186819e-14</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.000883755914401263</v>
+        <v>4.026011295177323e-14</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.003230355912819505</v>
+        <v>4.492442523670523e-14</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.001784405088983476</v>
+        <v>1.80348290012948e-13</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.0002544628805480897</v>
+        <v>3.246166356551949e-14</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.003938599955290556</v>
+        <v>9.660793622327454e-14</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0007824833737686276</v>
+        <v>3.544044398229307e-13</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0007572458707727492</v>
+        <v>4.53268641424729e-14</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.003348825266584754</v>
+        <v>4.224961851727327e-13</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.002875766484066844</v>
+        <v>9.719475387286874e-14</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0001678868575254455</v>
+        <v>1.589115937363633e-13</v>
       </c>
       <c r="CV10" t="n">
-        <v>5.950311606284231e-05</v>
+        <v>3.27506271614094e-14</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.002307607792317867</v>
+        <v>5.48710958668628e-14</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0007838534656912088</v>
+        <v>2.6722093776025e-14</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.001515356474556029</v>
+        <v>8.219334636733536e-14</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.150601721950807e-05</v>
+        <v>7.332313602852539e-14</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.001693304046057165</v>
+        <v>1.280964029781121e-14</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.001065360615029931</v>
+        <v>4.893824332320024e-14</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.0005927807651460171</v>
+        <v>6.803779273919369e-14</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0005795272882096469</v>
+        <v>3.158179284496604e-14</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.001207198249176145</v>
+        <v>1.239259075132976e-13</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.003053625812754035</v>
+        <v>3.856285408186666e-13</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.000685756211169064</v>
+        <v>1.895581673398705e-13</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.003918138332664967</v>
+        <v>5.171908975848578e-14</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.004594241268932819</v>
+        <v>7.72872841029934e-14</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.003550619818270206</v>
+        <v>1.980408567171799e-13</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.001496934914030135</v>
+        <v>6.838266389773417e-14</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.001532425987534225</v>
+        <v>1.360724412920872e-13</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.003124044742435217</v>
+        <v>2.904879028292617e-13</v>
       </c>
       <c r="DN10" t="n">
-        <v>3.614253364503384e-05</v>
+        <v>1.178764388615888e-13</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0003528256202116609</v>
+        <v>1.008388183609647e-13</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.00217953254468739</v>
+        <v>1.272671204533005e-13</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0001061904185917228</v>
+        <v>2.839672195846001e-14</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.001849082997068763</v>
+        <v>1.61584314721866e-13</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.002120444551110268</v>
+        <v>1.69469717122353e-13</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.001138623338192701</v>
+        <v>1.356868176843884e-13</v>
       </c>
       <c r="DU10" t="n">
-        <v>4.090504080522805e-05</v>
+        <v>1.76805781387096e-13</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0001010517298709601</v>
+        <v>2.510789970031069e-13</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.0004046792455483228</v>
+        <v>1.104616818479141e-13</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.001370430691167712</v>
+        <v>1.079799295225677e-14</v>
       </c>
       <c r="DY10" t="n">
-        <v>3.076449502259493e-05</v>
+        <v>2.847783315586272e-13</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.001581163727678359</v>
+        <v>1.407247257091682e-13</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.0008997475379146636</v>
+        <v>2.283956986211255e-13</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.00195467472076416</v>
+        <v>4.011010341681449e-14</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.0006867897463962436</v>
+        <v>2.028059930278894e-13</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.001180147053673863</v>
+        <v>2.064406994959841e-13</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.002292841672897339</v>
+        <v>1.458144314927384e-13</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0003166559035889804</v>
+        <v>1.34339682932548e-13</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.002795713255181909</v>
+        <v>7.499429137587665e-14</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.000699686526786536</v>
+        <v>3.19548668125183e-14</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0004613776109181345</v>
+        <v>2.105677320062092e-14</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0002034496574196965</v>
+        <v>3.521248098875898e-14</v>
       </c>
       <c r="EK10" t="n">
-        <v>7.40556642995216e-05</v>
+        <v>7.758005934714596e-14</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.001127070165239275</v>
+        <v>1.466744342084811e-13</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0008051415788941085</v>
+        <v>7.676602680351668e-14</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.000382119498681277</v>
+        <v>5.487354548614626e-14</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0004713787348009646</v>
+        <v>1.002932342752429e-13</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.001536766299977899</v>
+        <v>9.754677060135226e-15</v>
       </c>
       <c r="EQ10" t="n">
-        <v>8.300738409161568e-05</v>
+        <v>2.429091948202497e-14</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.001149981049820781</v>
+        <v>4.99726670634415e-14</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.001148786046542227</v>
+        <v>2.058352810028682e-13</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.001680694869719446</v>
+        <v>6.285156585721791e-14</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.001916631357744336</v>
+        <v>8.341348038719623e-14</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.002343041589483619</v>
+        <v>1.401427937456137e-13</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.0001310371444560587</v>
+        <v>1.317873151644548e-14</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.0003659366338979453</v>
+        <v>1.3363206822028e-14</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.002053272444754839</v>
+        <v>7.296511891864352e-14</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0002738366019912064</v>
+        <v>3.380585741896702e-14</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0006812938372604549</v>
+        <v>1.184268476469783e-13</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0002831816091202199</v>
+        <v>6.723334183226376e-14</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.001661864225752652</v>
+        <v>2.475470559603048e-14</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.001663619303144515</v>
+        <v>3.196334391825442e-14</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.0001833059795899317</v>
+        <v>7.502501495493946e-14</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.00115387118421495</v>
+        <v>3.313740612204824e-14</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0001612035412108526</v>
+        <v>2.748695097486847e-14</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0002534590312279761</v>
+        <v>1.357397945130415e-13</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.001045587006956339</v>
+        <v>5.142710733717186e-14</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.003044967539608479</v>
+        <v>2.319425576081946e-13</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0002434838825138286</v>
+        <v>3.23514069808413e-14</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.001103835529647768</v>
+        <v>2.345627761034946e-13</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.00117933948058635</v>
+        <v>7.147276883832585e-14</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0001369923702441156</v>
+        <v>1.284326784463038e-13</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.0003543998172972351</v>
+        <v>4.206457231148431e-13</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.001662676921114326</v>
+        <v>4.966197808889405e-13</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.002896954538300633</v>
+        <v>2.007065439410885e-13</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.001240292680449784</v>
+        <v>1.428162465675828e-13</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0005293364520184696</v>
+        <v>4.978510008760151e-13</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0004474756133276969</v>
+        <v>8.618256932754753e-13</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001031687948852777</v>
+        <v>1.191284755303751e-13</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.001672370359301567</v>
+        <v>6.181973742592703e-14</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0009903539903461933</v>
+        <v>5.497694855784163e-13</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.0001294342800974846</v>
+        <v>1.371775008038659e-13</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.002389420056715608</v>
+        <v>1.493300383521856e-13</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0006207975093275309</v>
+        <v>4.485715388003429e-14</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0003364645526744425</v>
+        <v>1.908219947072826e-13</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0003471832897048444</v>
+        <v>1.521418895814725e-13</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0004491369472816586</v>
+        <v>3.095109211244049e-14</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0006788399186916649</v>
+        <v>1.614680882489755e-13</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.003183242399245501</v>
+        <v>2.174028779266049e-13</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0002435478818370029</v>
+        <v>1.234650809324098e-13</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.000611366587691009</v>
+        <v>9.463491866231258e-14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3.141760680591688e-05</v>
+        <v>8.139593887790397e-09</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0001402696070726961</v>
+        <v>2.677398924788577e-08</v>
       </c>
       <c r="C11" t="n">
-        <v>2.220408714492805e-05</v>
+        <v>1.759706602655342e-09</v>
       </c>
       <c r="D11" t="n">
-        <v>9.233866876456887e-05</v>
+        <v>1.764710866325458e-08</v>
       </c>
       <c r="E11" t="n">
-        <v>5.47442541574128e-05</v>
+        <v>4.731479208430756e-09</v>
       </c>
       <c r="F11" t="n">
-        <v>4.283246016711928e-05</v>
+        <v>1.501442348228466e-08</v>
       </c>
       <c r="G11" t="n">
-        <v>1.567191793583333e-05</v>
+        <v>5.622724508214105e-09</v>
       </c>
       <c r="H11" t="n">
-        <v>7.9886223147696e-07</v>
+        <v>4.989356483520169e-09</v>
       </c>
       <c r="I11" t="n">
-        <v>8.651661119074561e-06</v>
+        <v>1.37614392103913e-10</v>
       </c>
       <c r="J11" t="n">
-        <v>5.364490061765537e-05</v>
+        <v>2.449506153467951e-10</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0001085830663214438</v>
+        <v>2.635481877177881e-08</v>
       </c>
       <c r="L11" t="n">
-        <v>1.694758611847647e-05</v>
+        <v>4.233706718537178e-09</v>
       </c>
       <c r="M11" t="n">
-        <v>6.12353251199238e-05</v>
+        <v>2.787735908782452e-08</v>
       </c>
       <c r="N11" t="n">
-        <v>6.187501276144758e-05</v>
+        <v>1.559605600220948e-08</v>
       </c>
       <c r="O11" t="n">
-        <v>7.761375309200957e-05</v>
+        <v>1.554799666791951e-08</v>
       </c>
       <c r="P11" t="n">
-        <v>2.495742046448868e-05</v>
+        <v>3.860663344568138e-09</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.176185444113798e-05</v>
+        <v>1.106857938637518e-09</v>
       </c>
       <c r="R11" t="n">
-        <v>2.969078650494339e-06</v>
+        <v>2.431242540623657e-09</v>
       </c>
       <c r="S11" t="n">
-        <v>6.57736472930992e-06</v>
+        <v>1.614716138576e-09</v>
       </c>
       <c r="T11" t="n">
-        <v>2.809387842717115e-05</v>
+        <v>3.295516304291368e-09</v>
       </c>
       <c r="U11" t="n">
-        <v>1.455120946047828e-05</v>
+        <v>7.376367072708945e-09</v>
       </c>
       <c r="V11" t="n">
-        <v>1.188430542242713e-05</v>
+        <v>7.97807597763267e-10</v>
       </c>
       <c r="W11" t="n">
-        <v>1.99818896362558e-05</v>
+        <v>6.340899361134689e-09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.815379073377699e-05</v>
+        <v>5.396035174243252e-09</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.532550570322201e-05</v>
+        <v>7.720937666988448e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.106805120798526e-05</v>
+        <v>4.461097269370384e-09</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.669629066076595e-05</v>
+        <v>2.140232879810355e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.272456398117356e-06</v>
+        <v>8.926837047340541e-10</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.034841261571273e-05</v>
+        <v>4.958415900091495e-09</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.10552455225843e-05</v>
+        <v>1.007401495556337e-09</v>
       </c>
       <c r="AE11" t="n">
-        <v>6.478781415353296e-06</v>
+        <v>7.671721036217605e-09</v>
       </c>
       <c r="AF11" t="n">
-        <v>6.72385431244038e-06</v>
+        <v>3.949653049062363e-09</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.269769427381107e-06</v>
+        <v>1.147682660018745e-08</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.926080403791275e-05</v>
+        <v>1.062794852124682e-09</v>
       </c>
       <c r="AI11" t="n">
-        <v>4.131297373533016e-06</v>
+        <v>1.205267974313529e-08</v>
       </c>
       <c r="AJ11" t="n">
-        <v>4.789416834682925e-06</v>
+        <v>1.514598002572143e-09</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.706899820419494e-05</v>
+        <v>2.309999080907232e-09</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.245307223347481e-05</v>
+        <v>4.030943578925417e-09</v>
       </c>
       <c r="AM11" t="n">
-        <v>8.609630640421528e-06</v>
+        <v>9.386138088984808e-09</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.812334858186659e-06</v>
+        <v>6.934161689287066e-09</v>
       </c>
       <c r="AO11" t="n">
-        <v>5.882128789380658e-06</v>
+        <v>5.809120295907633e-09</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.512795734015526e-06</v>
+        <v>5.610251374577047e-09</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.544174306734931e-06</v>
+        <v>9.238730891425462e-10</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.670669219805859e-06</v>
+        <v>5.218729892675356e-10</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.727744165691547e-05</v>
+        <v>1.277527750254137e-09</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.685528311820235e-06</v>
+        <v>1.52378842876999e-09</v>
       </c>
       <c r="AU11" t="n">
-        <v>9.087173384614289e-05</v>
+        <v>1.712540864673429e-08</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.157612470909953e-07</v>
+        <v>1.322449705298823e-08</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.978446718771011e-05</v>
+        <v>3.388307412421909e-10</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.272352437808877e-05</v>
+        <v>2.554126332654505e-08</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.357777339057066e-05</v>
+        <v>1.643132918616175e-08</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.97434757562587e-06</v>
+        <v>1.430187412942985e-09</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.347492525383132e-05</v>
+        <v>3.855063823721139e-09</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.138406464131549e-05</v>
+        <v>4.936862030291422e-11</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.812668233469594e-05</v>
+        <v>2.988319147689822e-09</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.489931284799241e-05</v>
+        <v>9.701214942481329e-09</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.323286702856421e-05</v>
+        <v>1.151295059287349e-09</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.402717589371605e-05</v>
+        <v>9.11162789662967e-09</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.636133962776512e-05</v>
+        <v>2.068485116524243e-08</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.032186966971494e-05</v>
+        <v>1.980607677865009e-09</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.714893414828111e-06</v>
+        <v>1.256793558113145e-09</v>
       </c>
       <c r="BJ11" t="n">
-        <v>2.722714089031797e-05</v>
+        <v>8.735314693808505e-09</v>
       </c>
       <c r="BK11" t="n">
-        <v>8.051060831348877e-06</v>
+        <v>1.199844112953485e-09</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.760316808940843e-05</v>
+        <v>8.570234522053966e-10</v>
       </c>
       <c r="BM11" t="n">
-        <v>2.350486283830833e-05</v>
+        <v>3.955142879874529e-09</v>
       </c>
       <c r="BN11" t="n">
-        <v>2.854416379705071e-05</v>
+        <v>1.208189659429593e-10</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.163760316558182e-05</v>
+        <v>5.408379522009454e-09</v>
       </c>
       <c r="BP11" t="n">
-        <v>8.553932275390252e-06</v>
+        <v>9.815012802505407e-09</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3.30512875734712e-07</v>
+        <v>6.712586042567636e-11</v>
       </c>
       <c r="BR11" t="n">
-        <v>1.124626942328177e-05</v>
+        <v>6.715328293438461e-10</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.845453183108475e-06</v>
+        <v>4.042560064476675e-09</v>
       </c>
       <c r="BT11" t="n">
-        <v>6.494702574855182e-06</v>
+        <v>2.991628722526229e-09</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.712181857437827e-06</v>
+        <v>5.408838932297044e-10</v>
       </c>
       <c r="BV11" t="n">
-        <v>4.487537444219925e-05</v>
+        <v>9.183715121707792e-09</v>
       </c>
       <c r="BW11" t="n">
-        <v>2.867263901862316e-05</v>
+        <v>7.577158456228972e-09</v>
       </c>
       <c r="BX11" t="n">
-        <v>1.589188650541473e-05</v>
+        <v>1.509804836707929e-09</v>
       </c>
       <c r="BY11" t="n">
-        <v>6.90943352310569e-06</v>
+        <v>5.042935402599369e-09</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.525814468550379e-06</v>
+        <v>9.598172923119819e-09</v>
       </c>
       <c r="CA11" t="n">
-        <v>2.2179741790751e-05</v>
+        <v>7.174399296872025e-09</v>
       </c>
       <c r="CB11" t="n">
-        <v>5.444419457489857e-07</v>
+        <v>5.130527114260985e-10</v>
       </c>
       <c r="CC11" t="n">
-        <v>1.948859244293999e-05</v>
+        <v>1.048308440054768e-09</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.584756884971284e-06</v>
+        <v>2.434723811450823e-10</v>
       </c>
       <c r="CE11" t="n">
-        <v>2.464931094436906e-05</v>
+        <v>8.915869820214084e-09</v>
       </c>
       <c r="CF11" t="n">
-        <v>1.935647560458165e-05</v>
+        <v>6.48010811676869e-11</v>
       </c>
       <c r="CG11" t="n">
-        <v>6.353532171488041e-06</v>
+        <v>6.018445297684138e-09</v>
       </c>
       <c r="CH11" t="n">
-        <v>3.094099383815774e-06</v>
+        <v>2.063661241891168e-09</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.052603874995839e-05</v>
+        <v>2.82974732535024e-09</v>
       </c>
       <c r="CJ11" t="n">
-        <v>3.517107188599766e-06</v>
+        <v>1.836222174311786e-09</v>
       </c>
       <c r="CK11" t="n">
-        <v>3.0089950087131e-06</v>
+        <v>2.179125768719814e-10</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.606298792466987e-05</v>
+        <v>2.001099952408936e-09</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.031571966654155e-05</v>
+        <v>6.932074470000771e-09</v>
       </c>
       <c r="CN11" t="n">
-        <v>6.630485586356372e-06</v>
+        <v>1.364256618785475e-08</v>
       </c>
       <c r="CO11" t="n">
-        <v>3.627935939221061e-06</v>
+        <v>1.264146298751712e-08</v>
       </c>
       <c r="CP11" t="n">
-        <v>3.306487269583158e-05</v>
+        <v>7.656608680406407e-09</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.309395495103672e-05</v>
+        <v>5.833811655975296e-09</v>
       </c>
       <c r="CR11" t="n">
-        <v>9.8178616099176e-06</v>
+        <v>1.246464487181242e-09</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.88849878415931e-05</v>
+        <v>5.766818578223365e-09</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.723534746313817e-06</v>
+        <v>5.069654029909998e-09</v>
       </c>
       <c r="CU11" t="n">
-        <v>3.462070253590355e-06</v>
+        <v>5.403710257034788e-10</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.65438268595608e-06</v>
+        <v>9.191011285381023e-10</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.143738856830169e-05</v>
+        <v>8.335635293121868e-09</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.771591996657662e-05</v>
+        <v>6.597636326155509e-10</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.549931766930968e-05</v>
+        <v>7.090428688627526e-09</v>
       </c>
       <c r="CZ11" t="n">
-        <v>7.901182470959611e-06</v>
+        <v>3.865762376875637e-09</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.260267163161188e-05</v>
+        <v>3.374746260220718e-09</v>
       </c>
       <c r="DB11" t="n">
-        <v>6.118656528997235e-06</v>
+        <v>2.196931525588752e-09</v>
       </c>
       <c r="DC11" t="n">
-        <v>5.231451723375358e-06</v>
+        <v>1.189236709109309e-09</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.174515728052938e-05</v>
+        <v>2.089043826813963e-09</v>
       </c>
       <c r="DE11" t="n">
-        <v>2.016041980823502e-05</v>
+        <v>4.717786161734239e-09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.066697041096631e-05</v>
+        <v>2.279098021418235e-09</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.539642264309805e-05</v>
+        <v>1.219643941396953e-09</v>
       </c>
       <c r="DH11" t="n">
-        <v>6.939200102351606e-05</v>
+        <v>5.574671835262279e-09</v>
       </c>
       <c r="DI11" t="n">
-        <v>3.729185482370667e-05</v>
+        <v>1.893422085785801e-09</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.255268671229715e-05</v>
+        <v>9.328283923082381e-09</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.085446562385187e-06</v>
+        <v>1.854701947578974e-10</v>
       </c>
       <c r="DL11" t="n">
-        <v>2.139598291250877e-05</v>
+        <v>1.064664356675848e-08</v>
       </c>
       <c r="DM11" t="n">
-        <v>2.187670816056198e-06</v>
+        <v>7.21596826736004e-09</v>
       </c>
       <c r="DN11" t="n">
-        <v>5.216013050812762e-06</v>
+        <v>9.302447701031724e-11</v>
       </c>
       <c r="DO11" t="n">
-        <v>9.903462341753766e-06</v>
+        <v>4.601258041248002e-09</v>
       </c>
       <c r="DP11" t="n">
-        <v>1.94277072296245e-05</v>
+        <v>2.447408942174434e-10</v>
       </c>
       <c r="DQ11" t="n">
-        <v>4.12067538491101e-06</v>
+        <v>3.310641094600442e-09</v>
       </c>
       <c r="DR11" t="n">
-        <v>2.189627139159711e-06</v>
+        <v>1.00888086773665e-09</v>
       </c>
       <c r="DS11" t="n">
-        <v>1.117980332310253e-06</v>
+        <v>2.46479081589257e-09</v>
       </c>
       <c r="DT11" t="n">
-        <v>1.439270249647961e-06</v>
+        <v>5.548802750610093e-09</v>
       </c>
       <c r="DU11" t="n">
-        <v>3.969465524278348e-06</v>
+        <v>6.771230687263596e-09</v>
       </c>
       <c r="DV11" t="n">
-        <v>2.730077903834172e-05</v>
+        <v>9.906204745391278e-10</v>
       </c>
       <c r="DW11" t="n">
-        <v>1.080950096365996e-05</v>
+        <v>3.528644043626628e-10</v>
       </c>
       <c r="DX11" t="n">
-        <v>1.546938074170612e-05</v>
+        <v>1.416830208711417e-09</v>
       </c>
       <c r="DY11" t="n">
-        <v>2.640634556883015e-05</v>
+        <v>4.930464037045112e-09</v>
       </c>
       <c r="DZ11" t="n">
-        <v>1.63940626407566e-06</v>
+        <v>5.716042306147529e-09</v>
       </c>
       <c r="EA11" t="n">
-        <v>1.266354956896976e-05</v>
+        <v>8.457415212603792e-09</v>
       </c>
       <c r="EB11" t="n">
-        <v>2.639887861732859e-05</v>
+        <v>8.870142398365033e-10</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.321789659414208e-05</v>
+        <v>1.998847087847366e-09</v>
       </c>
       <c r="ED11" t="n">
-        <v>5.052337655797601e-06</v>
+        <v>1.118930015309161e-08</v>
       </c>
       <c r="EE11" t="n">
-        <v>3.100807134615025e-06</v>
+        <v>4.445303680711277e-09</v>
       </c>
       <c r="EF11" t="n">
-        <v>1.177970716526033e-06</v>
+        <v>1.092675061542536e-09</v>
       </c>
       <c r="EG11" t="n">
-        <v>1.769581467669923e-05</v>
+        <v>3.230919531915788e-09</v>
       </c>
       <c r="EH11" t="n">
-        <v>1.041665655066026e-05</v>
+        <v>4.063617886629345e-09</v>
       </c>
       <c r="EI11" t="n">
-        <v>4.660469585360261e-06</v>
+        <v>5.565910399241147e-09</v>
       </c>
       <c r="EJ11" t="n">
-        <v>7.710189493081998e-06</v>
+        <v>3.358603395398063e-09</v>
       </c>
       <c r="EK11" t="n">
-        <v>8.315625564137008e-06</v>
+        <v>3.305796747454792e-09</v>
       </c>
       <c r="EL11" t="n">
-        <v>9.916169801726937e-06</v>
+        <v>2.805909060654699e-09</v>
       </c>
       <c r="EM11" t="n">
-        <v>5.569270342675736e-06</v>
+        <v>1.187233533705978e-09</v>
       </c>
       <c r="EN11" t="n">
-        <v>7.174165148171596e-06</v>
+        <v>7.927792866624372e-10</v>
       </c>
       <c r="EO11" t="n">
-        <v>2.126406343450071e-06</v>
+        <v>8.055365263714975e-10</v>
       </c>
       <c r="EP11" t="n">
-        <v>2.119696091540391e-06</v>
+        <v>5.110039502653763e-09</v>
       </c>
       <c r="EQ11" t="n">
-        <v>2.252848935313523e-05</v>
+        <v>2.268410126404774e-09</v>
       </c>
       <c r="ER11" t="n">
-        <v>2.012125150940847e-06</v>
+        <v>1.314086395254321e-09</v>
       </c>
       <c r="ES11" t="n">
-        <v>1.546405474073254e-05</v>
+        <v>3.807725690307961e-09</v>
       </c>
       <c r="ET11" t="n">
-        <v>2.243200015072944e-06</v>
+        <v>1.271108107658847e-09</v>
       </c>
       <c r="EU11" t="n">
-        <v>9.422723451280035e-06</v>
+        <v>1.286398987332404e-09</v>
       </c>
       <c r="EV11" t="n">
-        <v>3.82174075639341e-05</v>
+        <v>4.49238557465037e-09</v>
       </c>
       <c r="EW11" t="n">
-        <v>5.010462700738572e-06</v>
+        <v>5.585961027065878e-09</v>
       </c>
       <c r="EX11" t="n">
-        <v>1.66886707120284e-06</v>
+        <v>1.933738863479917e-10</v>
       </c>
       <c r="EY11" t="n">
-        <v>2.0277579096728e-05</v>
+        <v>9.680736212658303e-09</v>
       </c>
       <c r="EZ11" t="n">
-        <v>1.512256858404726e-05</v>
+        <v>5.878618702936933e-10</v>
       </c>
       <c r="FA11" t="n">
-        <v>1.063149102265015e-05</v>
+        <v>7.249934430575422e-09</v>
       </c>
       <c r="FB11" t="n">
-        <v>2.649557472977904e-06</v>
+        <v>7.453266892554211e-10</v>
       </c>
       <c r="FC11" t="n">
-        <v>1.03082284113043e-05</v>
+        <v>2.264561205223004e-09</v>
       </c>
       <c r="FD11" t="n">
-        <v>8.349209565494675e-06</v>
+        <v>8.304923415636267e-10</v>
       </c>
       <c r="FE11" t="n">
-        <v>2.005220494538662e-06</v>
+        <v>1.43800493734858e-09</v>
       </c>
       <c r="FF11" t="n">
-        <v>1.774031079548877e-05</v>
+        <v>1.826941931071246e-10</v>
       </c>
       <c r="FG11" t="n">
-        <v>1.07657160697272e-05</v>
+        <v>8.648465832372665e-10</v>
       </c>
       <c r="FH11" t="n">
-        <v>2.640865659486735e-06</v>
+        <v>5.426787907936159e-09</v>
       </c>
       <c r="FI11" t="n">
-        <v>3.043008837266825e-05</v>
+        <v>1.8542252178122e-09</v>
       </c>
       <c r="FJ11" t="n">
-        <v>2.535272142267786e-05</v>
+        <v>4.451797597226914e-09</v>
       </c>
       <c r="FK11" t="n">
-        <v>3.400049536139704e-06</v>
+        <v>1.917075609370045e-09</v>
       </c>
       <c r="FL11" t="n">
-        <v>1.08531257865252e-05</v>
+        <v>2.245846397741502e-09</v>
       </c>
       <c r="FM11" t="n">
-        <v>6.679396392428316e-06</v>
+        <v>7.718189420913291e-10</v>
       </c>
       <c r="FN11" t="n">
-        <v>2.924137334048282e-05</v>
+        <v>2.508760976738245e-09</v>
       </c>
       <c r="FO11" t="n">
-        <v>1.948113276739605e-05</v>
+        <v>1.003462202220362e-08</v>
       </c>
       <c r="FP11" t="n">
-        <v>4.097482815268449e-07</v>
+        <v>9.049885285605797e-10</v>
       </c>
       <c r="FQ11" t="n">
-        <v>6.282400136115029e-06</v>
+        <v>1.005869432191275e-08</v>
       </c>
       <c r="FR11" t="n">
-        <v>9.612276699044742e-06</v>
+        <v>9.063197303760262e-09</v>
       </c>
       <c r="FS11" t="n">
-        <v>7.646155609108973e-06</v>
+        <v>3.618563670926278e-09</v>
       </c>
       <c r="FT11" t="n">
-        <v>3.657477282104082e-05</v>
+        <v>1.058296028588757e-08</v>
       </c>
       <c r="FU11" t="n">
-        <v>3.538176542861038e-06</v>
+        <v>5.324703789000296e-09</v>
       </c>
       <c r="FV11" t="n">
-        <v>2.568611307651736e-05</v>
+        <v>7.33790628260067e-09</v>
       </c>
       <c r="FW11" t="n">
-        <v>1.629996404517442e-05</v>
+        <v>4.528248886970232e-09</v>
       </c>
       <c r="FX11" t="n">
-        <v>5.297175448504277e-06</v>
+        <v>1.82075465815501e-09</v>
       </c>
       <c r="FY11" t="n">
-        <v>4.257894397596829e-05</v>
+        <v>1.358929635486561e-09</v>
       </c>
       <c r="FZ11" t="n">
-        <v>1.496547702117823e-05</v>
+        <v>4.859053159833593e-10</v>
       </c>
       <c r="GA11" t="n">
-        <v>2.020110969169764e-06</v>
+        <v>7.387745526443723e-09</v>
       </c>
       <c r="GB11" t="n">
-        <v>1.080263427866157e-05</v>
+        <v>4.427699096254401e-09</v>
       </c>
       <c r="GC11" t="n">
-        <v>3.388885670574382e-05</v>
+        <v>5.086272736321007e-09</v>
       </c>
       <c r="GD11" t="n">
-        <v>1.58861257659737e-05</v>
+        <v>1.396438964462732e-08</v>
       </c>
       <c r="GE11" t="n">
-        <v>5.500574479810894e-05</v>
+        <v>8.624676084423299e-09</v>
       </c>
       <c r="GF11" t="n">
-        <v>1.073285147867864e-06</v>
+        <v>6.337454450111579e-10</v>
       </c>
       <c r="GG11" t="n">
-        <v>1.295463789574569e-05</v>
+        <v>5.561403004783472e-10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.05828778445720673</v>
+        <v>0.0004407293745316565</v>
       </c>
       <c r="B12" t="n">
-        <v>1.032274723052979</v>
+        <v>0.04678390920162201</v>
       </c>
       <c r="C12" t="n">
-        <v>0.07731351256370544</v>
+        <v>0.02647748030722141</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8335562348365784</v>
+        <v>0.0007302071899175644</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2264892309904099</v>
+        <v>0.02007041685283184</v>
       </c>
       <c r="F12" t="n">
-        <v>1.445080757141113</v>
+        <v>0.1387812048196793</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2562276721000671</v>
+        <v>0.01086700521409512</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5071274042129517</v>
+        <v>0.05633106455206871</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2248750627040863</v>
+        <v>0.0008984480518847704</v>
       </c>
       <c r="J12" t="n">
-        <v>0.03928125649690628</v>
+        <v>0.01363618113100529</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9575725197792053</v>
+        <v>0.07016437500715256</v>
       </c>
       <c r="L12" t="n">
-        <v>0.06066367402672768</v>
+        <v>0.04568298161029816</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5583878755569458</v>
+        <v>0.006000192370265722</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1510520577430725</v>
+        <v>0.03738108277320862</v>
       </c>
       <c r="O12" t="n">
-        <v>1.001802921295166</v>
+        <v>0.1646851599216461</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3613103926181793</v>
+        <v>0.01445646211504936</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4989633560180664</v>
+        <v>0.05870510637760162</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2721885442733765</v>
+        <v>0.01789845339953899</v>
       </c>
       <c r="S12" t="n">
-        <v>0.03634821623563766</v>
+        <v>0.00310873705893755</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01648294180631638</v>
+        <v>0.01176031585782766</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1785753071308136</v>
+        <v>0.01608758606016636</v>
       </c>
       <c r="V12" t="n">
-        <v>0.462245762348175</v>
+        <v>0.011419378221035</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4759755432605743</v>
+        <v>0.005941296461969614</v>
       </c>
       <c r="X12" t="n">
-        <v>0.04987729340791702</v>
+        <v>0.02151417173445225</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.05168990045785904</v>
+        <v>0.01054268516600132</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.06205131858587265</v>
+        <v>0.01264175213873386</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.07686521112918854</v>
+        <v>0.009804626926779747</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.04138186946511269</v>
+        <v>0.007965340279042721</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.05848587676882744</v>
+        <v>0.01916667446494102</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1944673806428909</v>
+        <v>0.003292372450232506</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.1943529844284058</v>
+        <v>0.02065623737871647</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2567835450172424</v>
+        <v>0.02059091441333294</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.3202367722988129</v>
+        <v>0.02764681726694107</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.1315177083015442</v>
+        <v>0.003915996290743351</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.1700911521911621</v>
+        <v>0.04781890287995338</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.2109250873327255</v>
+        <v>0.005598187912255526</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.05726976692676544</v>
+        <v>0.005723430775105953</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.005626935511827469</v>
+        <v>0.01724756695330143</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.1872263103723526</v>
+        <v>0.008839691057801247</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.1058280169963837</v>
+        <v>0.002966931322589517</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.1921633183956146</v>
+        <v>0.01231835689395666</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.2140324115753174</v>
+        <v>0.01650609821081161</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.02742433175444603</v>
+        <v>0.0118129625916481</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.2196280509233475</v>
+        <v>0.01752404496073723</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.08301989734172821</v>
+        <v>0.00698592234402895</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.1613644659519196</v>
+        <v>0.007540292572230101</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.5064846277236938</v>
+        <v>0.08916573226451874</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.093146912753582</v>
+        <v>0.03282708302140236</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.4294924139976501</v>
+        <v>0.007314403541386127</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.6266686320304871</v>
+        <v>0.0076956981793046</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.9114980697631836</v>
+        <v>0.113605223596096</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.1274397820234299</v>
+        <v>0.01408521831035614</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.01561275869607925</v>
+        <v>0.02858759090304375</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.3093899488449097</v>
+        <v>0.00681012962013483</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.07039877772331238</v>
+        <v>0.008558626286685467</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.2268911600112915</v>
+        <v>0.02390454895794392</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.01506334915757179</v>
+        <v>0.01668455451726913</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.4179045557975769</v>
+        <v>0.02297195233404636</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.177394837141037</v>
+        <v>0.01071835029870272</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.2840591669082642</v>
+        <v>0.01391734927892685</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.08210490643978119</v>
+        <v>0.0143999420106411</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.07937400043010712</v>
+        <v>0.01992533914744854</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.001391887664794922</v>
+        <v>0.006232746876776218</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.001199524849653244</v>
+        <v>0.01044781412929296</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.205441802740097</v>
+        <v>0.0298954676836729</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.02176786959171295</v>
+        <v>0.0163729153573513</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.3364204168319702</v>
+        <v>0.007937607355415821</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1502502262592316</v>
+        <v>0.02166085876524448</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.06377676874399185</v>
+        <v>0.0188642181456089</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.06664314866065979</v>
+        <v>0.01430253032594919</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.3860396146774292</v>
+        <v>0.01493240520358086</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.4005379676818848</v>
+        <v>0.02153578214347363</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.08584430068731308</v>
+        <v>0.001120417262427509</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.4266930818557739</v>
+        <v>0.04109146445989609</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.108310654759407</v>
+        <v>0.01044251210987568</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.3012525141239166</v>
+        <v>0.01629951223731041</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.2106797993183136</v>
+        <v>0.0073911570943892</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.4004164040088654</v>
+        <v>0.06115948408842087</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.0239136815071106</v>
+        <v>0.01589184254407883</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.05657587945461273</v>
+        <v>0.01090903114527464</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.1113974526524544</v>
+        <v>0.002443633275106549</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.03190153837203979</v>
+        <v>0.002356569282710552</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.1403239667415619</v>
+        <v>0.01655601337552071</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.01541095227003098</v>
+        <v>0.004841036163270473</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.1334145218133926</v>
+        <v>0.003284413833171129</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.06578663736581802</v>
+        <v>0.005379093810915947</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.2576237618923187</v>
+        <v>0.03545752912759781</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.06719452142715454</v>
+        <v>0.01031622663140297</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.1529729813337326</v>
+        <v>0.007444713730365038</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.009522987529635429</v>
+        <v>0.007219522260129452</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.03803488612174988</v>
+        <v>0.007922347635030746</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.08680061995983124</v>
+        <v>0.022554537281394</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.03430730849504471</v>
+        <v>0.02734345197677612</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.2188086807727814</v>
+        <v>0.01019904296845198</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.5643162727355957</v>
+        <v>0.006348824594169855</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.09748639166355133</v>
+        <v>0.004146814346313477</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0147789865732193</v>
+        <v>0.01747588440775871</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.2064262181520462</v>
+        <v>0.009471574798226357</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.2323952615261078</v>
+        <v>0.01486641634255648</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.007303124759346247</v>
+        <v>0.004849916789680719</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.1466313302516937</v>
+        <v>0.01416549924761057</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.03612838312983513</v>
+        <v>0.009344693273305893</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.1231118440628052</v>
+        <v>0.001738556078635156</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.1233341544866562</v>
+        <v>0.01231158152222633</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.2987595200538635</v>
+        <v>0.03864878043532372</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.07802796363830566</v>
+        <v>0.005472376476973295</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.2782875299453735</v>
+        <v>0.01021162420511246</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.08335375040769577</v>
+        <v>0.006087023299187422</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.04829713702201843</v>
+        <v>0.01208425499498844</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.5859572291374207</v>
+        <v>0.02851631864905357</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.1199692264199257</v>
+        <v>0.006323407404124737</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.4941429197788239</v>
+        <v>0.01671154983341694</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.3401657044887543</v>
+        <v>0.01415219902992249</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.3121704161167145</v>
+        <v>0.02648422122001648</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.00930553674697876</v>
+        <v>0.01262809894979</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.3088798224925995</v>
+        <v>0.02453307062387466</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.3331363201141357</v>
+        <v>0.02147645503282547</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.08212700486183167</v>
+        <v>0.0006072293035686016</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.001502044498920441</v>
+        <v>0.001536776777356863</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.09078671038150787</v>
+        <v>0.0030886335298419</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.3160783648490906</v>
+        <v>0.01353531889617443</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.1554447859525681</v>
+        <v>0.007613484282046556</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.2475040853023529</v>
+        <v>0.01902697794139385</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1115934923291206</v>
+        <v>0.01324185915291309</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.09128785878419876</v>
+        <v>0.006841377355158329</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.0374477319419384</v>
+        <v>0.02316004224121571</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.07175754010677338</v>
+        <v>0.00541648780927062</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.07800023257732391</v>
+        <v>0.01846451684832573</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.1572427749633789</v>
+        <v>0.02753391861915588</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.1052975654602051</v>
+        <v>0.001494188560172915</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.03475979343056679</v>
+        <v>0.005824076477438211</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.04514800012111664</v>
+        <v>0.007564194034785032</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.03363190591335297</v>
+        <v>0.007679057773202658</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.2524112164974213</v>
+        <v>0.01925349794328213</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.157370001077652</v>
+        <v>0.020233990624547</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.02297697216272354</v>
+        <v>0.0002258688909932971</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.1065016612410545</v>
+        <v>0.003458628430962563</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.1139813810586929</v>
+        <v>0.004747928585857153</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.2104741036891937</v>
+        <v>0.00154173607006669</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.1369761079549789</v>
+        <v>0.004588950891047716</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.2015834450721741</v>
+        <v>0.01997126825153828</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.01382012665271759</v>
+        <v>0.007603859528899193</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.1761066317558289</v>
+        <v>0.004201404750347137</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.01735077984631062</v>
+        <v>0.002037411089986563</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.01720202714204788</v>
+        <v>0.006088940892368555</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.09906590729951859</v>
+        <v>0.01379550062119961</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.1062202677130699</v>
+        <v>0.00545917171984911</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.2048096060752869</v>
+        <v>0.008803117088973522</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.0182754322886467</v>
+        <v>0.007781975902616978</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.1038248687982559</v>
+        <v>0.01629504002630711</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.001500807702541351</v>
+        <v>0.01261566951870918</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.2100051045417786</v>
+        <v>0.001646506716497242</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.117534764111042</v>
+        <v>6.608548574149609e-05</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.0187930054962635</v>
+        <v>0.005736518185585737</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.1135907992720604</v>
+        <v>0.01847832463681698</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.00466490164399147</v>
+        <v>0.004857403691858053</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.1282444894313812</v>
+        <v>0.001454847515560687</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.06894632428884506</v>
+        <v>0.003532773349434137</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.2341757416725159</v>
+        <v>0.03506463393568993</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.08642196655273438</v>
+        <v>0.01168742310255766</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.1987238675355911</v>
+        <v>0.007192006800323725</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.04707863554358482</v>
+        <v>0.0008703386411070824</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.01187767460942268</v>
+        <v>0.00902483519166708</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.242865726351738</v>
+        <v>0.004827972501516342</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.1394075006246567</v>
+        <v>0.01460246182978153</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.1267779022455215</v>
+        <v>0.01268770918250084</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.03772581368684769</v>
+        <v>0.004304423462599516</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.1374140530824661</v>
+        <v>0.03467949107289314</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.0720476508140564</v>
+        <v>0.0111457696184516</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.1806319355964661</v>
+        <v>0.01493094302713871</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.1906027048826218</v>
+        <v>0.04338424280285835</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.1337402909994125</v>
+        <v>0.01246514730155468</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.3339680433273315</v>
+        <v>0.008733969181776047</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.3793964982032776</v>
+        <v>0.0129898339509964</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01697370037436485</v>
+        <v>0.02470618300139904</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.02617448195815086</v>
+        <v>0.01907433569431305</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.04074344411492348</v>
+        <v>0.005291239358484745</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.2626897692680359</v>
+        <v>0.003440421307459474</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.0354175940155983</v>
+        <v>0.03739131987094879</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.2552717328071594</v>
+        <v>0.01079235784709454</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.02362006902694702</v>
+        <v>0.003971946891397238</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.05950506031513214</v>
+        <v>0.001782633829861879</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.06057345122098923</v>
+        <v>0.03307823836803436</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.09611828625202179</v>
+        <v>0.007718790788203478</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.7391660809516907</v>
+        <v>0.05893157050013542</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.09843231737613678</v>
+        <v>0.02649573050439358</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.4068680107593536</v>
+        <v>0.02361596003174782</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.1475949138402939</v>
+        <v>0.00803074985742569</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.03587320446968079</v>
+        <v>0.004721383564174175</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.4620141386985779</v>
+        <v>0.1129587665200233</v>
       </c>
       <c r="B13" t="n">
-        <v>0.06186456233263016</v>
+        <v>0.01635837554931641</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03708164393901825</v>
+        <v>0.09196779876947403</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1586993932723999</v>
+        <v>0.004486363381147385</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1976279616355896</v>
+        <v>0.1133741289377213</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4702726304531097</v>
+        <v>0.1357860565185547</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05646360665559769</v>
+        <v>0.03329413384199142</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1816825419664383</v>
+        <v>0.08061482012271881</v>
       </c>
       <c r="I13" t="n">
-        <v>0.01857221685349941</v>
+        <v>0.01010544132441282</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4025181531906128</v>
+        <v>0.1361044496297836</v>
       </c>
       <c r="K13" t="n">
-        <v>0.05786646157503128</v>
+        <v>0.03620921447873116</v>
       </c>
       <c r="L13" t="n">
-        <v>0.007887200452387333</v>
+        <v>0.1149791404604912</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02210341766476631</v>
+        <v>0.009166531264781952</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2301007807254791</v>
+        <v>0.103217139840126</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3820555508136749</v>
+        <v>0.1989962756633759</v>
       </c>
       <c r="P13" t="n">
-        <v>0.08571562170982361</v>
+        <v>0.06844625622034073</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.1368269175291061</v>
+        <v>0.1075067594647408</v>
       </c>
       <c r="R13" t="n">
-        <v>0.03707582131028175</v>
+        <v>0.04302645102143288</v>
       </c>
       <c r="S13" t="n">
-        <v>0.03180879727005959</v>
+        <v>0.008695287629961967</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1361236125230789</v>
+        <v>0.01116239838302135</v>
       </c>
       <c r="U13" t="n">
-        <v>0.02118083089590073</v>
+        <v>0.04377152770757675</v>
       </c>
       <c r="V13" t="n">
-        <v>0.144364133477211</v>
+        <v>0.01557119376957417</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1769948750734329</v>
+        <v>0.01902519352734089</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1056993901729584</v>
+        <v>0.01531795784831047</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1005979031324387</v>
+        <v>0.02100001275539398</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.07543205469846725</v>
+        <v>0.002557358471676707</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.06150265038013458</v>
+        <v>0.01012387871742249</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.01913935877382755</v>
+        <v>0.01910107210278511</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.03838637471199036</v>
+        <v>0.009303892031311989</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.07509028911590576</v>
+        <v>0.04444735869765282</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.04862024262547493</v>
+        <v>0.01294693723320961</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.06342068314552307</v>
+        <v>0.005075949709862471</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01762874610722065</v>
+        <v>0.002114006783813238</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.03099272027611732</v>
+        <v>0.03643476963043213</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0640050396323204</v>
+        <v>0.004487842787057161</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.02788265608251095</v>
+        <v>0.02674231305718422</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.1025646030902863</v>
+        <v>0.003984907642006874</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.03621301800012589</v>
+        <v>0.01373642217367887</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.05395006388425827</v>
+        <v>0.007510981522500515</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.01685748994350433</v>
+        <v>0.02092370577156544</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.04502630606293678</v>
+        <v>0.01881011761724949</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.05667875334620476</v>
+        <v>0.01694455742835999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.02091974392533302</v>
+        <v>0.01344994269311428</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.08107706159353256</v>
+        <v>0.01154262945055962</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.03832266479730606</v>
+        <v>0.007285642437636852</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.3030514121055603</v>
+        <v>0.1197622716426849</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.04352150857448578</v>
+        <v>0.06933723390102386</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.04063612967729568</v>
+        <v>0.07623117417097092</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.1187630295753479</v>
+        <v>0.02348047122359276</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.2163375914096832</v>
+        <v>0.04989121854305267</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.2623383402824402</v>
+        <v>0.1200564652681351</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.03209250792860985</v>
+        <v>0.01573779061436653</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.06953899562358856</v>
+        <v>0.04242353513836861</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.02500230260193348</v>
+        <v>0.003627636469900608</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.06259936094284058</v>
+        <v>0.02820097655057907</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.06897559762001038</v>
+        <v>0.0527038499712944</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.03366526961326599</v>
+        <v>2.721085911616683e-05</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.1498932838439941</v>
+        <v>0.03691926226019859</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.06816698610782623</v>
+        <v>0.05697896704077721</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.07480014115571976</v>
+        <v>0.01719400100409985</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.07165428996086121</v>
+        <v>0.002900179475545883</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.03908325731754303</v>
+        <v>0.02185853756964207</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01336616463959217</v>
+        <v>0.0143401250243187</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.01507986895740032</v>
+        <v>0.02814037166535854</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.007466837763786316</v>
+        <v>0.05940322950482368</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.05441693216562271</v>
+        <v>0.06730746477842331</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.06026095896959305</v>
+        <v>0.0206945389509201</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.008119844831526279</v>
+        <v>0.02180841192603111</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.05389319360256195</v>
+        <v>0.016364810988307</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.008067745715379715</v>
+        <v>0.02131838724017143</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.02872718498110771</v>
+        <v>0.02206968329846859</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.07406431436538696</v>
+        <v>0.00641938392072916</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.1199311539530754</v>
+        <v>0.04329495877027512</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.03449849039316177</v>
+        <v>0.02653558366000652</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.06384940445423126</v>
+        <v>0.03940409049391747</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.006330709904432297</v>
+        <v>0.02101948298513889</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.1375896483659744</v>
+        <v>0.02559152618050575</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.1951685398817062</v>
+        <v>0.06535211950540543</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.01812656596302986</v>
+        <v>0.02516221441328526</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.05385740101337433</v>
+        <v>0.02182542905211449</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.03415421396493912</v>
+        <v>0.01715145073831081</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.08370736241340637</v>
+        <v>0.02264209650456905</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.1076380535960197</v>
+        <v>0.01144680660218</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.001202032435685396</v>
+        <v>0.02241281233727932</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.03538349643349648</v>
+        <v>0.01010852865874767</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.08307504653930664</v>
+        <v>0.02159523218870163</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.07619424164295197</v>
+        <v>0.03033533506095409</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.00464249961078167</v>
+        <v>0.01378530636429787</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.1168601810932159</v>
+        <v>5.239748861640692e-05</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.008191738277673721</v>
+        <v>0.001737439073622227</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.01440634857863188</v>
+        <v>0.005480925552546978</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.01224574819207191</v>
+        <v>0.002540158107876778</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.02387152053415775</v>
+        <v>0.0002418076619505882</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.07474929094314575</v>
+        <v>0.02134571969509125</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.22770956158638</v>
+        <v>0.01706710830330849</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.03350784629583359</v>
+        <v>0.001772714778780937</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.0002895817160606384</v>
+        <v>0.04737770557403564</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.05271048843860626</v>
+        <v>0.02630561031401157</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.04366669431328773</v>
+        <v>0.01625288836658001</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0789584144949913</v>
+        <v>0.02842788957059383</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.0902300700545311</v>
+        <v>0.01809044741094112</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.008094970136880875</v>
+        <v>0.02895468659698963</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.01646277494728565</v>
+        <v>0.01008149515837431</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.07264228910207748</v>
+        <v>0.03666460514068604</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.09106047451496124</v>
+        <v>0.03293372318148613</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.02879450097680092</v>
+        <v>0.01116516347974539</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.1102890074253082</v>
+        <v>0.002831547288224101</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.01071169413626194</v>
+        <v>0.004459747113287449</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.07421465218067169</v>
+        <v>0.008854541927576065</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.02590508200228214</v>
+        <v>0.04972429573535919</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.05056918039917946</v>
+        <v>0.06025301665067673</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.1851641833782196</v>
+        <v>0.03007829561829567</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06733355671167374</v>
+        <v>0.01517280749976635</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.03889459744095802</v>
+        <v>0.0009609339758753777</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.07345309853553772</v>
+        <v>0.02144400402903557</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.1859031617641449</v>
+        <v>0.002180555602535605</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.09127786755561829</v>
+        <v>0.04063967242836952</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.01482219435274601</v>
+        <v>0.0008559804409742355</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.007364343851804733</v>
+        <v>0.02754731103777885</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.0364600345492363</v>
+        <v>0.01627607829868793</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.004313305020332336</v>
+        <v>0.006361358799040318</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03892112523317337</v>
+        <v>0.03503905236721039</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.1011761277914047</v>
+        <v>0.03806367889046669</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.06643827259540558</v>
+        <v>0.01763378456234932</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.1215092018246651</v>
+        <v>0.01400802005082369</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.002167873550206423</v>
+        <v>0.02507493831217289</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.004777450580149889</v>
+        <v>0.00186488963663578</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.03534052148461342</v>
+        <v>0.01950929686427116</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.005357523448765278</v>
+        <v>0.01879645511507988</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.1441434323787689</v>
+        <v>0.07443311810493469</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0981767326593399</v>
+        <v>0.0195893794298172</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.129682332277298</v>
+        <v>0.03272807225584984</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.004486341029405594</v>
+        <v>0.0001256980467587709</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.01100588217377663</v>
+        <v>0.007292204536497593</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.1036668941378593</v>
+        <v>0.02064976654946804</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.06366397440433502</v>
+        <v>0.007698698900640011</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.08694557845592499</v>
+        <v>0.006423359736800194</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.01992702484130859</v>
+        <v>0.0332501046359539</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.01404883898794651</v>
+        <v>0.03955715149641037</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.06750854849815369</v>
+        <v>0.03264458477497101</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.03663577884435654</v>
+        <v>0.01663541421294212</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.004224898293614388</v>
+        <v>0.008900880813598633</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.07217882573604584</v>
+        <v>0.01413291972130537</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0420006550848484</v>
+        <v>0.002908159513026476</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.06277971714735031</v>
+        <v>0.01712521351873875</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.1049443855881691</v>
+        <v>0.01456375606358051</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.06992676109075546</v>
+        <v>0.006373576819896698</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.03667139634490013</v>
+        <v>0.004007436335086823</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01297304779291153</v>
+        <v>0.02216330915689468</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0293758288025856</v>
+        <v>0.04449354112148285</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.1448430716991425</v>
+        <v>0.04048487544059753</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.07182396203279495</v>
+        <v>0.03732645511627197</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.08277338743209839</v>
+        <v>0.006200873758643866</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.07055158913135529</v>
+        <v>0.02804115600883961</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.06993547827005386</v>
+        <v>0.01050883810967207</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.01135544199496508</v>
+        <v>0.02169723622500896</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.007134786807000637</v>
+        <v>0.004994239658117294</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.07099199295043945</v>
+        <v>0.02512823790311813</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.07518377900123596</v>
+        <v>0.03906558081507683</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.002404753118753433</v>
+        <v>0.02239036001265049</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.1252670586109161</v>
+        <v>0.001371141872368753</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.00332585908472538</v>
+        <v>0.00257562380284071</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.04648804664611816</v>
+        <v>0.04084227606654167</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.005879610776901245</v>
+        <v>0.01917259581387043</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.01139554008841515</v>
+        <v>0.030518539249897</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.1374040395021439</v>
+        <v>0.05428116768598557</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.07734041661024094</v>
+        <v>0.03167424723505974</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.08250366896390915</v>
+        <v>0.03677842766046524</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.06858719140291214</v>
+        <v>0.01581579074263573</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.05528266727924347</v>
+        <v>0.04113350436091423</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.01644735224545002</v>
+        <v>0.01009128522127867</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.1014112308621407</v>
+        <v>0.03688380122184753</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.02872876264154911</v>
+        <v>0.1233560368418694</v>
       </c>
       <c r="FR13" t="n">
-        <v>5.652103573083878e-05</v>
+        <v>0.05861524492502213</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.01425683777779341</v>
+        <v>0.007367956452071667</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.02780087664723396</v>
+        <v>0.001481355633586645</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.05401448905467987</v>
+        <v>0.03979280218482018</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.1333298832178116</v>
+        <v>0.01594085618853569</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.01154249161481857</v>
+        <v>0.02785030007362366</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.07400567829608917</v>
+        <v>0.02416549064218998</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.05602271854877472</v>
+        <v>0.012153091840446</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.03540061041712761</v>
+        <v>0.02447273954749107</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.01841411553323269</v>
+        <v>0.06441628187894821</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01319612190127373</v>
+        <v>0.002578329760581255</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.1366993188858032</v>
+        <v>0.02527021430432796</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.001503288745880127</v>
+        <v>0.01022365316748619</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.03222444653511047</v>
+        <v>0.03423991799354553</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.04447659105062485</v>
+        <v>0.01735271513462067</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.00404975563287735</v>
+        <v>0.01252073515206575</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1.771107054082677e-05</v>
+        <v>0.03885792195796967</v>
       </c>
       <c r="B14" t="n">
-        <v>6.076517456676811e-05</v>
+        <v>0.0592382401227951</v>
       </c>
       <c r="C14" t="n">
-        <v>2.129363338099211e-06</v>
+        <v>0.08631095290184021</v>
       </c>
       <c r="D14" t="n">
-        <v>3.023803037649486e-05</v>
+        <v>0.04085562378168106</v>
       </c>
       <c r="E14" t="n">
-        <v>8.640044143248815e-06</v>
+        <v>0.07202491164207458</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0001048721896950155</v>
+        <v>0.1728125959634781</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1281370461802e-05</v>
+        <v>0.04755973443388939</v>
       </c>
       <c r="H14" t="n">
-        <v>5.466636139317416e-05</v>
+        <v>0.005962062627077103</v>
       </c>
       <c r="I14" t="n">
-        <v>1.851393608376384e-05</v>
+        <v>0.02960295602679253</v>
       </c>
       <c r="J14" t="n">
-        <v>2.736589340202045e-05</v>
+        <v>0.03036915138363838</v>
       </c>
       <c r="K14" t="n">
-        <v>5.302171484800056e-05</v>
+        <v>0.05409425869584084</v>
       </c>
       <c r="L14" t="n">
-        <v>1.201733630296076e-05</v>
+        <v>0.1412632167339325</v>
       </c>
       <c r="M14" t="n">
-        <v>4.450226697372273e-06</v>
+        <v>0.005420789122581482</v>
       </c>
       <c r="N14" t="n">
-        <v>2.57660576608032e-05</v>
+        <v>0.1981720626354218</v>
       </c>
       <c r="O14" t="n">
-        <v>9.070278611034155e-05</v>
+        <v>0.2509142160415649</v>
       </c>
       <c r="P14" t="n">
-        <v>1.533807153464295e-05</v>
+        <v>0.04700412601232529</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.546204243320972e-05</v>
+        <v>0.03799797222018242</v>
       </c>
       <c r="R14" t="n">
-        <v>1.233801685884828e-05</v>
+        <v>0.02160965465009212</v>
       </c>
       <c r="S14" t="n">
-        <v>6.667824891337659e-06</v>
+        <v>0.02403956651687622</v>
       </c>
       <c r="T14" t="n">
-        <v>2.10764028452104e-08</v>
+        <v>0.002513797953724861</v>
       </c>
       <c r="U14" t="n">
-        <v>5.92355854678317e-06</v>
+        <v>0.04283946752548218</v>
       </c>
       <c r="V14" t="n">
-        <v>3.001589720952325e-05</v>
+        <v>0.02997291460633278</v>
       </c>
       <c r="W14" t="n">
-        <v>3.832591391983442e-05</v>
+        <v>0.01897796057164669</v>
       </c>
       <c r="X14" t="n">
-        <v>6.312920049822424e-06</v>
+        <v>0.07004829496145248</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.420584223727928e-06</v>
+        <v>0.01682949997484684</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.392550752323586e-06</v>
+        <v>0.05754804983735085</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.150286597199738e-06</v>
+        <v>0.06586668640375137</v>
       </c>
       <c r="AB14" t="n">
-        <v>8.334774975082837e-06</v>
+        <v>0.08950568735599518</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.450399607478175e-06</v>
+        <v>0.0249914675951004</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.955912118020933e-06</v>
+        <v>0.01138032227754593</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.553420927142724e-06</v>
+        <v>0.05282541364431381</v>
       </c>
       <c r="AF14" t="n">
-        <v>4.596035068971105e-06</v>
+        <v>0.08480308949947357</v>
       </c>
       <c r="AG14" t="n">
-        <v>8.041912224143744e-06</v>
+        <v>0.04094966873526573</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.632397010733257e-06</v>
+        <v>0.05728386715054512</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.268573942070361e-05</v>
+        <v>0.03885890170931816</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.239456469193101e-05</v>
+        <v>0.002878166735172272</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.476034594816156e-05</v>
+        <v>0.03933514654636383</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.387430984323146e-06</v>
+        <v>0.02411206439137459</v>
       </c>
       <c r="AM14" t="n">
-        <v>6.195127298269654e-06</v>
+        <v>0.03061501681804657</v>
       </c>
       <c r="AN14" t="n">
-        <v>9.519688319414854e-06</v>
+        <v>0.02963458746671677</v>
       </c>
       <c r="AO14" t="n">
-        <v>2.769314733086503e-07</v>
+        <v>0.03676524758338928</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.264668000862002e-05</v>
+        <v>0.03930847719311714</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.709389264055062e-06</v>
+        <v>0.008530293591320515</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.568719421309652e-06</v>
+        <v>0.01697450876235962</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.738019588832685e-07</v>
+        <v>0.03335512802004814</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.766252535162494e-05</v>
+        <v>0.03228826075792313</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.288032843964174e-05</v>
+        <v>0.1442269831895828</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.41957207233645e-05</v>
+        <v>0.02647119574248791</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.616951860545669e-05</v>
+        <v>0.009623246267437935</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.173425496555865e-06</v>
+        <v>0.04691658169031143</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.416563751874492e-05</v>
+        <v>0.2135506868362427</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.279520231240895e-05</v>
+        <v>0.05596790462732315</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.116762152581941e-05</v>
+        <v>0.03153971955180168</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.248637181561207e-05</v>
+        <v>0.02025685831904411</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.195505774376215e-06</v>
+        <v>0.05529480427503586</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.856164873170201e-06</v>
+        <v>0.08921764045953751</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.11071603896562e-05</v>
+        <v>0.08141317963600159</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.405214607075322e-05</v>
+        <v>0.03127310425043106</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.774492481374182e-06</v>
+        <v>0.05788035318255424</v>
       </c>
       <c r="BH14" t="n">
-        <v>3.854179522022605e-05</v>
+        <v>0.003597798757255077</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.945492633443791e-05</v>
+        <v>0.01072987634688616</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.161607087851735e-05</v>
+        <v>0.002898939419537783</v>
       </c>
       <c r="BK14" t="n">
-        <v>1.180311119242106e-05</v>
+        <v>0.1122555434703827</v>
       </c>
       <c r="BL14" t="n">
-        <v>6.708308319502976e-06</v>
+        <v>0.00344877690076828</v>
       </c>
       <c r="BM14" t="n">
-        <v>2.196561217715498e-05</v>
+        <v>0.01107076928019524</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.359546695312019e-05</v>
+        <v>0.06518317759037018</v>
       </c>
       <c r="BO14" t="n">
-        <v>4.607467872119742e-06</v>
+        <v>0.02540480718016624</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.054026365134632e-07</v>
+        <v>0.03762815892696381</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.37366134065087e-06</v>
+        <v>0.009782031178474426</v>
       </c>
       <c r="BR14" t="n">
-        <v>1.332838110101875e-06</v>
+        <v>0.02569085359573364</v>
       </c>
       <c r="BS14" t="n">
-        <v>1.169597453554161e-06</v>
+        <v>0.0008700927719473839</v>
       </c>
       <c r="BT14" t="n">
-        <v>2.155640686396509e-06</v>
+        <v>0.06088041514158249</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.379409236003994e-06</v>
+        <v>0.01755428686738014</v>
       </c>
       <c r="BV14" t="n">
-        <v>2.485011100361589e-05</v>
+        <v>0.06266893446445465</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.455708105728263e-06</v>
+        <v>0.01456002332270145</v>
       </c>
       <c r="BX14" t="n">
-        <v>2.304596819158178e-05</v>
+        <v>0.01010961551219225</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.735862861096393e-05</v>
+        <v>0.03123581409454346</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.611221705388743e-05</v>
+        <v>0.1365822106599808</v>
       </c>
       <c r="CA14" t="n">
-        <v>1.544596307212487e-05</v>
+        <v>0.01022937521338463</v>
       </c>
       <c r="CB14" t="n">
-        <v>8.950921255745925e-06</v>
+        <v>0.01017247326672077</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.151682408817578e-05</v>
+        <v>0.01445835269987583</v>
       </c>
       <c r="CD14" t="n">
-        <v>8.428300475316064e-07</v>
+        <v>0.01459978055208921</v>
       </c>
       <c r="CE14" t="n">
-        <v>7.022000318102073e-06</v>
+        <v>0.02313557080924511</v>
       </c>
       <c r="CF14" t="n">
-        <v>1.792643615772249e-06</v>
+        <v>0.02866236120462418</v>
       </c>
       <c r="CG14" t="n">
-        <v>9.106526704272255e-06</v>
+        <v>0.00773739255964756</v>
       </c>
       <c r="CH14" t="n">
-        <v>2.283353751408868e-06</v>
+        <v>0.02673038467764854</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.754410368448589e-05</v>
+        <v>0.06145030632615089</v>
       </c>
       <c r="CJ14" t="n">
-        <v>8.044173227972351e-06</v>
+        <v>0.01911891810595989</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.216973760165274e-05</v>
+        <v>0.00781365018337965</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.340261971767177e-06</v>
+        <v>0.03861593082547188</v>
       </c>
       <c r="CM14" t="n">
-        <v>9.717061402625404e-06</v>
+        <v>0.007344008889049292</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.311087908106856e-05</v>
+        <v>0.01078827865421772</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.196753601107048e-06</v>
+        <v>0.02262292243540287</v>
       </c>
       <c r="CP14" t="n">
-        <v>3.870138607453555e-05</v>
+        <v>0.0634232684969902</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.424865670036525e-05</v>
+        <v>0.08869858086109161</v>
       </c>
       <c r="CR14" t="n">
-        <v>4.158632236794801e-06</v>
+        <v>0.1383251845836639</v>
       </c>
       <c r="CS14" t="n">
-        <v>9.032385605678428e-06</v>
+        <v>0.01668857783079147</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.718878360814415e-08</v>
+        <v>0.05303023010492325</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.489019177824957e-05</v>
+        <v>0.01004244945943356</v>
       </c>
       <c r="CV14" t="n">
-        <v>6.255378366404329e-07</v>
+        <v>0.009475941769778728</v>
       </c>
       <c r="CW14" t="n">
-        <v>9.418137778993696e-06</v>
+        <v>0.02578458189964294</v>
       </c>
       <c r="CX14" t="n">
-        <v>4.625117981049698e-06</v>
+        <v>0.02137136459350586</v>
       </c>
       <c r="CY14" t="n">
-        <v>6.129218490968924e-06</v>
+        <v>0.003447308670729399</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.4679059151822e-07</v>
+        <v>0.0470445305109024</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.388997017988004e-05</v>
+        <v>0.06823419779539108</v>
       </c>
       <c r="DB14" t="n">
-        <v>7.296985131688416e-06</v>
+        <v>0.0082139503210783</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.433711531717563e-05</v>
+        <v>0.0143763218075037</v>
       </c>
       <c r="DD14" t="n">
-        <v>5.803132808068767e-06</v>
+        <v>0.03351150453090668</v>
       </c>
       <c r="DE14" t="n">
-        <v>4.201602678222116e-06</v>
+        <v>0.05306247994303703</v>
       </c>
       <c r="DF14" t="n">
-        <v>3.112408012384549e-05</v>
+        <v>0.0248519703745842</v>
       </c>
       <c r="DG14" t="n">
-        <v>5.068689006293425e-07</v>
+        <v>0.01485034823417664</v>
       </c>
       <c r="DH14" t="n">
-        <v>4.13337183999829e-05</v>
+        <v>0.01999691128730774</v>
       </c>
       <c r="DI14" t="n">
-        <v>6.443528400268406e-05</v>
+        <v>0.09093165397644043</v>
       </c>
       <c r="DJ14" t="n">
-        <v>5.239512393018231e-05</v>
+        <v>0.03820079565048218</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.6047073333757e-06</v>
+        <v>0.01908251829445362</v>
       </c>
       <c r="DL14" t="n">
-        <v>1.8805911167874e-05</v>
+        <v>0.008071606978774071</v>
       </c>
       <c r="DM14" t="n">
-        <v>1.365244497719686e-05</v>
+        <v>0.0176826436072588</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.906846591737121e-07</v>
+        <v>0.04548045992851257</v>
       </c>
       <c r="DO14" t="n">
-        <v>4.902184628008399e-06</v>
+        <v>0.08160870522260666</v>
       </c>
       <c r="DP14" t="n">
-        <v>5.269617304293206e-06</v>
+        <v>0.0104061234742403</v>
       </c>
       <c r="DQ14" t="n">
-        <v>9.37098593567498e-06</v>
+        <v>0.04207112267613411</v>
       </c>
       <c r="DR14" t="n">
-        <v>2.647159817570355e-05</v>
+        <v>0.04002629965543747</v>
       </c>
       <c r="DS14" t="n">
-        <v>4.861857632931788e-06</v>
+        <v>0.05442214757204056</v>
       </c>
       <c r="DT14" t="n">
-        <v>2.742366632446647e-05</v>
+        <v>0.01316133514046669</v>
       </c>
       <c r="DU14" t="n">
-        <v>4.066863766638562e-06</v>
+        <v>0.04397448152303696</v>
       </c>
       <c r="DV14" t="n">
-        <v>2.19520770770032e-05</v>
+        <v>0.02201623842120171</v>
       </c>
       <c r="DW14" t="n">
-        <v>6.901721462782007e-06</v>
+        <v>0.0007332423701882362</v>
       </c>
       <c r="DX14" t="n">
-        <v>4.830118541576667e-06</v>
+        <v>0.0738184005022049</v>
       </c>
       <c r="DY14" t="n">
-        <v>1.511477785243187e-05</v>
+        <v>0.02843228913843632</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.661706275830511e-06</v>
+        <v>0.01748442463576794</v>
       </c>
       <c r="EA14" t="n">
-        <v>1.384567076456733e-05</v>
+        <v>0.01240148209035397</v>
       </c>
       <c r="EB14" t="n">
-        <v>6.599413609365001e-06</v>
+        <v>0.06532293558120728</v>
       </c>
       <c r="EC14" t="n">
-        <v>5.165865786693757e-06</v>
+        <v>0.03619001805782318</v>
       </c>
       <c r="ED14" t="n">
-        <v>9.419429261470214e-06</v>
+        <v>0.01990291103720665</v>
       </c>
       <c r="EE14" t="n">
-        <v>3.908277903974522e-06</v>
+        <v>0.0002053957432508469</v>
       </c>
       <c r="EF14" t="n">
-        <v>3.37860956278746e-06</v>
+        <v>0.006783538963645697</v>
       </c>
       <c r="EG14" t="n">
-        <v>7.165378065110417e-06</v>
+        <v>0.01782573387026787</v>
       </c>
       <c r="EH14" t="n">
-        <v>6.644895165663911e-06</v>
+        <v>0.005970250815153122</v>
       </c>
       <c r="EI14" t="n">
-        <v>6.484712685050908e-06</v>
+        <v>0.01862374506890774</v>
       </c>
       <c r="EJ14" t="n">
-        <v>1.678145963524003e-05</v>
+        <v>0.07013100385665894</v>
       </c>
       <c r="EK14" t="n">
-        <v>3.292931432952173e-05</v>
+        <v>0.03411976248025894</v>
       </c>
       <c r="EL14" t="n">
-        <v>1.944279802046367e-06</v>
+        <v>0.0211636945605278</v>
       </c>
       <c r="EM14" t="n">
-        <v>6.090964234317653e-06</v>
+        <v>0.006723584141582251</v>
       </c>
       <c r="EN14" t="n">
-        <v>3.525378815538716e-06</v>
+        <v>0.01626186072826385</v>
       </c>
       <c r="EO14" t="n">
-        <v>8.153254498211027e-07</v>
+        <v>0.01995468884706497</v>
       </c>
       <c r="EP14" t="n">
-        <v>2.101075779137318e-06</v>
+        <v>0.007226694375276566</v>
       </c>
       <c r="EQ14" t="n">
-        <v>6.337138529488584e-06</v>
+        <v>0.0198546014726162</v>
       </c>
       <c r="ER14" t="n">
-        <v>6.108290108386427e-06</v>
+        <v>0.02390754967927933</v>
       </c>
       <c r="ES14" t="n">
-        <v>3.271200057497481e-06</v>
+        <v>0.06570214778184891</v>
       </c>
       <c r="ET14" t="n">
-        <v>4.905706191493664e-06</v>
+        <v>0.1023240312933922</v>
       </c>
       <c r="EU14" t="n">
-        <v>1.163181150332093e-05</v>
+        <v>0.06502354145050049</v>
       </c>
       <c r="EV14" t="n">
-        <v>2.279034197272267e-05</v>
+        <v>0.0330229178071022</v>
       </c>
       <c r="EW14" t="n">
-        <v>1.925160722748842e-05</v>
+        <v>0.04438246414065361</v>
       </c>
       <c r="EX14" t="n">
-        <v>2.900721938203787e-07</v>
+        <v>0.02040992677211761</v>
       </c>
       <c r="EY14" t="n">
-        <v>5.337989477993688e-06</v>
+        <v>0.03101939707994461</v>
       </c>
       <c r="EZ14" t="n">
-        <v>4.575978891807608e-06</v>
+        <v>0.01707099564373493</v>
       </c>
       <c r="FA14" t="n">
-        <v>8.671717296238057e-06</v>
+        <v>0.006801237352192402</v>
       </c>
       <c r="FB14" t="n">
-        <v>2.326476760572405e-06</v>
+        <v>0.02872315607964993</v>
       </c>
       <c r="FC14" t="n">
-        <v>1.94402728084242e-05</v>
+        <v>0.0621861144900322</v>
       </c>
       <c r="FD14" t="n">
-        <v>4.518336936598644e-06</v>
+        <v>0.02091081067919731</v>
       </c>
       <c r="FE14" t="n">
-        <v>1.10491937448387e-05</v>
+        <v>0.003655252046883106</v>
       </c>
       <c r="FF14" t="n">
-        <v>6.903306257299846e-06</v>
+        <v>0.02865800075232983</v>
       </c>
       <c r="FG14" t="n">
-        <v>3.19759601552505e-06</v>
+        <v>0.003393745981156826</v>
       </c>
       <c r="FH14" t="n">
-        <v>1.391923797200434e-05</v>
+        <v>0.07840388268232346</v>
       </c>
       <c r="FI14" t="n">
-        <v>1.508104560343781e-05</v>
+        <v>0.003220003098249435</v>
       </c>
       <c r="FJ14" t="n">
-        <v>8.322919711645227e-06</v>
+        <v>0.02552388980984688</v>
       </c>
       <c r="FK14" t="n">
-        <v>1.248357239092002e-05</v>
+        <v>0.05440868064761162</v>
       </c>
       <c r="FL14" t="n">
-        <v>9.934092304320075e-06</v>
+        <v>0.08416295796632767</v>
       </c>
       <c r="FM14" t="n">
-        <v>7.360018571489491e-06</v>
+        <v>0.003484111279249191</v>
       </c>
       <c r="FN14" t="n">
-        <v>9.006499567476567e-06</v>
+        <v>0.008784164674580097</v>
       </c>
       <c r="FO14" t="n">
-        <v>8.146863365254831e-06</v>
+        <v>0.04447273164987564</v>
       </c>
       <c r="FP14" t="n">
-        <v>6.505769761133706e-06</v>
+        <v>0.001741748303174973</v>
       </c>
       <c r="FQ14" t="n">
-        <v>1.580403841217048e-05</v>
+        <v>0.09085580706596375</v>
       </c>
       <c r="FR14" t="n">
-        <v>2.03833533305442e-05</v>
+        <v>0.07972149550914764</v>
       </c>
       <c r="FS14" t="n">
-        <v>2.167720595025457e-06</v>
+        <v>0.1360297948122025</v>
       </c>
       <c r="FT14" t="n">
-        <v>5.710825462301727e-06</v>
+        <v>0.08221887797117233</v>
       </c>
       <c r="FU14" t="n">
-        <v>1.054224230756517e-05</v>
+        <v>0.07010985165834427</v>
       </c>
       <c r="FV14" t="n">
-        <v>7.475686743418919e-06</v>
+        <v>0.1243539229035378</v>
       </c>
       <c r="FW14" t="n">
-        <v>3.021164957317524e-05</v>
+        <v>0.01598666608333588</v>
       </c>
       <c r="FX14" t="n">
-        <v>6.119006684457418e-06</v>
+        <v>0.03383707255125046</v>
       </c>
       <c r="FY14" t="n">
-        <v>3.615905825427035e-06</v>
+        <v>0.02640881389379501</v>
       </c>
       <c r="FZ14" t="n">
-        <v>3.711669705808163e-06</v>
+        <v>0.01824997738003731</v>
       </c>
       <c r="GA14" t="n">
-        <v>1.218612851516809e-05</v>
+        <v>0.003804272040724754</v>
       </c>
       <c r="GB14" t="n">
-        <v>8.68239931151038e-06</v>
+        <v>0.02611250057816505</v>
       </c>
       <c r="GC14" t="n">
-        <v>3.727625880856067e-05</v>
+        <v>0.01279057655483484</v>
       </c>
       <c r="GD14" t="n">
-        <v>1.168606104329228e-05</v>
+        <v>0.02524080127477646</v>
       </c>
       <c r="GE14" t="n">
-        <v>1.6867012163857e-05</v>
+        <v>0.00186579953879118</v>
       </c>
       <c r="GF14" t="n">
-        <v>4.121538040635642e-06</v>
+        <v>0.004669100977480412</v>
       </c>
       <c r="GG14" t="n">
-        <v>1.993136902456172e-05</v>
+        <v>0.02967559359967709</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.003685906995087862</v>
+        <v>9.365989535581321e-05</v>
       </c>
       <c r="B15" t="n">
-        <v>0.02656074985861778</v>
+        <v>0.00187536352314055</v>
       </c>
       <c r="C15" t="n">
-        <v>0.007725244387984276</v>
+        <v>2.582647721283138e-05</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0004534553736448288</v>
+        <v>0.002171548316255212</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01473842281848192</v>
+        <v>0.0009210969437845051</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00491251889616251</v>
+        <v>0.002023920882493258</v>
       </c>
       <c r="G15" t="n">
-        <v>0.006465485319495201</v>
+        <v>0.001255440409295261</v>
       </c>
       <c r="H15" t="n">
-        <v>0.006202749907970428</v>
+        <v>0.001843572361394763</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0006227793055586517</v>
+        <v>0.0008101018029265106</v>
       </c>
       <c r="J15" t="n">
-        <v>0.005669586826115847</v>
+        <v>0.0003034602268598974</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01630185544490814</v>
+        <v>0.002540521323680878</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005249870009720325</v>
+        <v>0.0004726118058897555</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0002391358721069992</v>
+        <v>0.003081812988966703</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01582073047757149</v>
+        <v>0.001732282107695937</v>
       </c>
       <c r="O15" t="n">
-        <v>0.004452756606042385</v>
+        <v>0.002421489916741848</v>
       </c>
       <c r="P15" t="n">
-        <v>0.002598324324935675</v>
+        <v>0.001323555363342166</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.001592726446688175</v>
+        <v>0.0002077027602354065</v>
       </c>
       <c r="R15" t="n">
-        <v>0.001382614718750119</v>
+        <v>0.0003752107149921358</v>
       </c>
       <c r="S15" t="n">
-        <v>0.001810436835512519</v>
+        <v>0.0002020518586505204</v>
       </c>
       <c r="T15" t="n">
-        <v>0.007876114919781685</v>
+        <v>0.000226808144361712</v>
       </c>
       <c r="U15" t="n">
-        <v>0.001674520783126354</v>
+        <v>0.0005325487582013011</v>
       </c>
       <c r="V15" t="n">
-        <v>0.006844913586974144</v>
+        <v>0.0006636133184656501</v>
       </c>
       <c r="W15" t="n">
-        <v>0.002502632094547153</v>
+        <v>0.0006328842719085515</v>
       </c>
       <c r="X15" t="n">
-        <v>0.003292069304734468</v>
+        <v>0.0005465378635562956</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.004291582386940718</v>
+        <v>5.990537465550005e-05</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.001707197283394635</v>
+        <v>0.0003472263633739203</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0008725424413569272</v>
+        <v>0.0002890380274038762</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.004705519415438175</v>
+        <v>0.0001035402674460784</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.01189396157860756</v>
+        <v>0.001108467578887939</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.003960129339247942</v>
+        <v>3.11688709189184e-05</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.001218004385009408</v>
+        <v>0.0009748978773131967</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.002611338393762708</v>
+        <v>0.001363853341899812</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.001566614490002394</v>
+        <v>0.0004513172025326639</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.003892174921929836</v>
+        <v>0.0002579827269073576</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.005193182732909918</v>
+        <v>0.001086885342374444</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.001146307680755854</v>
+        <v>0.0004412356356624514</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.002799371723085642</v>
+        <v>0.0003319175157230347</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.004327026195824146</v>
+        <v>0.0006250019068829715</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.00250014872290194</v>
+        <v>0.0005735235754400492</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.007212486118078232</v>
+        <v>0.001047181314788759</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.002906354842707515</v>
+        <v>0.000636346114333719</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.001991481054574251</v>
+        <v>1.559455267852172e-05</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.001980176893994212</v>
+        <v>0.000476037326734513</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.001139382249675691</v>
+        <v>0.001103416900150478</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.00189542374573648</v>
+        <v>5.545552994590253e-06</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.0009771093027666211</v>
+        <v>0.0003675514308270067</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.02254494465887547</v>
+        <v>0.003532961243763566</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.006241960451006889</v>
+        <v>0.00048870436148718</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.009239848703145981</v>
+        <v>0.001640307018533349</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.003805747255682945</v>
+        <v>0.002052090829238296</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.005362299270927906</v>
+        <v>0.001487681292928755</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.006045563146471977</v>
+        <v>0.0001551975146867335</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.002165562706068158</v>
+        <v>0.0003700564848259091</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.004215891938656569</v>
+        <v>7.853742863517255e-05</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.0004864868242293596</v>
+        <v>0.0001670321216806769</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.004906278103590012</v>
+        <v>0.0003363827418070287</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.0005161179578863084</v>
+        <v>0.0001341440220130607</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.002733023371547461</v>
+        <v>0.0005061535630375147</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.01031842082738876</v>
+        <v>0.001028322032652795</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.001660592621192336</v>
+        <v>9.120965842157602e-05</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.001047339290380478</v>
+        <v>0.0004702384467236698</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.002382329665124416</v>
+        <v>0.001181520521640778</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.001573838177137077</v>
+        <v>0.0006446025217883289</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.0009697008063085377</v>
+        <v>0.0001512966700829566</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.008509248495101929</v>
+        <v>0.001659265602938831</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.001483430969528854</v>
+        <v>0.0002123093436239287</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.0007808915688656271</v>
+        <v>0.0004753152607008815</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.007710393983870745</v>
+        <v>0.0007144617266021669</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01292391866445541</v>
+        <v>8.219863229896873e-05</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.002688859356567264</v>
+        <v>0.001683251233771443</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.007507032249122858</v>
+        <v>0.0001349912636214867</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.008905378170311451</v>
+        <v>0.0003999903565272689</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.002367074135690928</v>
+        <v>0.0005141274305060506</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.01257972419261932</v>
+        <v>0.001599497860297561</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.004981811624020338</v>
+        <v>0.0002642532926984131</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.001936089247465134</v>
+        <v>0.001226485706865788</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.0008454393246211112</v>
+        <v>0.001121245208196342</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.003041826421394944</v>
+        <v>0.0007917724433355033</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.002793675055727363</v>
+        <v>0.0006631476571783423</v>
       </c>
       <c r="CB15" t="n">
-        <v>1.539662480354309e-05</v>
+        <v>0.0003548305248841643</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.0005314710433594882</v>
+        <v>0.0004711025394499302</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.0001969161094166338</v>
+        <v>0.0001103801623685285</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.004009077325463295</v>
+        <v>0.0005306809325702488</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.000368005596101284</v>
+        <v>2.062039675365668e-05</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.002480405615642667</v>
+        <v>0.0008377917110919952</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.0009961746400222182</v>
+        <v>0.0003409216878935695</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.908863669086713e-05</v>
+        <v>0.0003080924798268825</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.0002756098401732743</v>
+        <v>0.0002255811705254018</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.0008288294775411487</v>
+        <v>0.0003789012262132019</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.0004477215989027172</v>
+        <v>1.259438249689993e-05</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.006012678146362305</v>
+        <v>0.001031554769724607</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.00760758388787508</v>
+        <v>0.001599228708073497</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.003402343485504389</v>
+        <v>0.0006949355592951179</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.003668498946353793</v>
+        <v>0.002320652827620506</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.01045392174273729</v>
+        <v>4.48599093942903e-05</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.004888030700385571</v>
+        <v>2.790422149701044e-05</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.004702904727309942</v>
+        <v>0.0007916698232293129</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.0002871054457500577</v>
+        <v>0.0005132204969413579</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.00554241705685854</v>
+        <v>0.0003966640506405383</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.0005547740729525685</v>
+        <v>0.0002768121194094419</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.003077868605032563</v>
+        <v>0.0003932926920242608</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.00130423391237855</v>
+        <v>1.454626908525825e-05</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.003476632293313742</v>
+        <v>0.001011769403703511</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.0008091205381788313</v>
+        <v>0.0001441682252334431</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.001542984275147319</v>
+        <v>0.0004530815058387816</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.0003454693942330778</v>
+        <v>9.520449384581298e-05</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.001035858993418515</v>
+        <v>0.0002266231458634138</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.001030150684528053</v>
+        <v>8.374135359190404e-05</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.004963444545865059</v>
+        <v>0.0005419538356363773</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.007833486422896385</v>
+        <v>0.0001068471174221486</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.004544216208159924</v>
+        <v>0.0006973274284973741</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.009550740942358971</v>
+        <v>0.0003475776757113636</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.01072119828313589</v>
+        <v>0.0007507356349378824</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.01314006466418505</v>
+        <v>0.001157362246885896</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.01079048588871956</v>
+        <v>0.0006676650955341756</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.003472746349871159</v>
+        <v>0.0006609365809708834</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.008341545239090919</v>
+        <v>8.270333637483418e-06</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.002227065153419971</v>
+        <v>0.0002649351954460144</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.003955969586968422</v>
+        <v>8.668232476338744e-05</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.002106131752952933</v>
+        <v>2.290847623953596e-05</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.005707096308469772</v>
+        <v>0.0003667671117000282</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.007871371693909168</v>
+        <v>0.0001893356384243816</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.0003750736941583455</v>
+        <v>0.0006803181022405624</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.0005159317515790462</v>
+        <v>0.000356986653059721</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.003861744655296206</v>
+        <v>0.0008694952703081071</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.002564519410952926</v>
+        <v>0.0006971716647967696</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.0002686413645278662</v>
+        <v>0.0002353532618144527</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.006797668524086475</v>
+        <v>2.691962436074391e-05</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.004080591723322868</v>
+        <v>0.0002350942377233878</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.0001132353572756983</v>
+        <v>0.001248829998075962</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.003568552434444427</v>
+        <v>0.0001460481871617958</v>
       </c>
       <c r="EB15" t="n">
-        <v>8.056290971580893e-05</v>
+        <v>0.0002346757682971656</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.001008617226034403</v>
+        <v>0.0002262304478790611</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.003171913325786591</v>
+        <v>0.001076090033166111</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.004865601193159819</v>
+        <v>0.001086643780581653</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.000707610510289669</v>
+        <v>0.00016813947877381</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.00345859257504344</v>
+        <v>0.0004334549303166568</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.0009495051926933229</v>
+        <v>0.0001189343311125413</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.003941829316318035</v>
+        <v>0.0005433209589682519</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.001859334763139486</v>
+        <v>0.0003259822842665017</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.001380769535899162</v>
+        <v>0.0006790378247387707</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.000195892178453505</v>
+        <v>0.000368374225217849</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.004811919294297695</v>
+        <v>4.638151949620806e-05</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.0004104450054001063</v>
+        <v>0.0001233448274433613</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.00280852010473609</v>
+        <v>0.0005835385527461767</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.003484925488010049</v>
+        <v>0.0003310955071356148</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.003078676061704755</v>
+        <v>0.0002740365453064442</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.007713446393609047</v>
+        <v>0.0004671611823141575</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.004212573170661926</v>
+        <v>0.0002724004443734884</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.002059287391602993</v>
+        <v>0.0008197153802029788</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.001197786652483046</v>
+        <v>5.976960528641939e-05</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.003376623382791877</v>
+        <v>2.95277141049155e-06</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.001560511183924973</v>
+        <v>0.0008808941347524524</v>
       </c>
       <c r="EX15" t="n">
-        <v>9.910308290272951e-05</v>
+        <v>0.0001709714997559786</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.003850505454465747</v>
+        <v>0.0007331069791689515</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.0004292891244404018</v>
+        <v>5.674930434906855e-05</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.002464303513988853</v>
+        <v>0.0009410441853106022</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.0001061761358869262</v>
+        <v>7.779263978591189e-05</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.002270752796903253</v>
+        <v>0.0004714519891422242</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.0001704058959148824</v>
+        <v>0.0002366195694776252</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.001350817852653563</v>
+        <v>0.0002797114138957113</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.0003617270849645138</v>
+        <v>0.0002086832100758329</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.001493696589022875</v>
+        <v>1.347549550700933e-05</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.0002760432253126055</v>
+        <v>0.0006645841640420258</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.00370260258205235</v>
+        <v>0.0005219593876972795</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.0058637335896492</v>
+        <v>0.0005396574269980192</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.004576794803142548</v>
+        <v>0.000554471742361784</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.004764541052281857</v>
+        <v>0.0003377934626769274</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.0008200157899409533</v>
+        <v>0.0006172943976707757</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.001116851810365915</v>
+        <v>0.0008042301051318645</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.001067595556378365</v>
+        <v>0.0007126847631298006</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.002055930206552148</v>
+        <v>0.0006599443149752915</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.00358660495840013</v>
+        <v>0.0002260580513393506</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.0001624039723537862</v>
+        <v>0.001711480552330613</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.0032211784273386</v>
+        <v>0.001819584402255714</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.001866691396571696</v>
+        <v>0.00248411763459444</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.002526269294321537</v>
+        <v>0.0008309835102409124</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.002818831475451589</v>
+        <v>0.0002472274354659021</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.001512799877673388</v>
+        <v>0.001299618976190686</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.01114427112042904</v>
+        <v>0.0009381712879985571</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.006531447172164917</v>
+        <v>0.0003467965289019048</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.000120462296763435</v>
+        <v>0.0006712688482366502</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.001957599306479096</v>
+        <v>0.0001926652766996995</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.006242253351956606</v>
+        <v>0.0003939506714232266</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.006670425646007061</v>
+        <v>0.0004968980210833251</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.007586331106722355</v>
+        <v>0.001114468788728118</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.005073958542197943</v>
+        <v>0.0008699150057509542</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.007479419000446796</v>
+        <v>0.0008645734051242471</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.002397544449195266</v>
+        <v>0.0001762445754138753</v>
       </c>
     </row>
   </sheetData>
